--- a/exports/styled_report.xlsx
+++ b/exports/styled_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <color rgb="00F1F1F1"/>
@@ -1068,7 +1065,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1076,227 +1073,218 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="127" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="141" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="142" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="143" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="123" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="129" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="60" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="144" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="145" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="95" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="146" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="73" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="98" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="147" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="148" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="149" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="150" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="151" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="152" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="153" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="154" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="62" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="155" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="156" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="157" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="158" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="132" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="64" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="67" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="56" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="159" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="57" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="160" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="58" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="161" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="115" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="63" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="137" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="68" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="65" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="139" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="66" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="162" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="124" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="70" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="163" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="127" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="45" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="141" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="142" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="143" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="123" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="129" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="60" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="144" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="145" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="95" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="146" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="73" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="98" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="147" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="148" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="149" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="150" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="151" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="152" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="87" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="153" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="154" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="62" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="89" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="155" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="156" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="49" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="92" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="44" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="157" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="158" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="48" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="132" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="72" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="76" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="88" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="64" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="67" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="56" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="159" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="57" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="160" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="58" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="161" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="59" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="115" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="63" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="137" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="68" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="65" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="139" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="66" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="82" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="162" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="124" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="70" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="163" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="164" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="74" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="110" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="133" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="165" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="166" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="102" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="114" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="79" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="167" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="80" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="168" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="135" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="169" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="120" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="170" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="84" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="171" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="104" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="172" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="85" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="173" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="174" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="128" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="175" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="176" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="177" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="178" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="179" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="180" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="181" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="182" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="96" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="97" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="99" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="183" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="100" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="184" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="101" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="185" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="117" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="186" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="187" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="188" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="189" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="103" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="190" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="105" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="106" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="191" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="140" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="192" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="193" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="111" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="112" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="194" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="113" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="195" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="196" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="116" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="138" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="197" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="198" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="118" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="199" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="200" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="201" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="119" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="202" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="121" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="122" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="203" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="125" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="126" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="204" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="130" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="131" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="205" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="134" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="206" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="136" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="164" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="74" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="110" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="133" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="75" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="90" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="165" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="166" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="102" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="77" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="114" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="78" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="79" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="167" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="80" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="168" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="135" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="83" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="169" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="120" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="170" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="84" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="171" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="104" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="172" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="85" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="86" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="173" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="174" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="128" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="175" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="176" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="177" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="93" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="178" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="179" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="94" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="180" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="181" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="182" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="96" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="97" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="99" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="183" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="100" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="184" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="101" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="185" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="117" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="186" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="187" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="188" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="189" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="103" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="190" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="105" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="106" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="191" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="140" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="192" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="193" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="111" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="112" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="194" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="113" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="195" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="196" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="116" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="138" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="197" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="198" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="118" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="199" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="200" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="201" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="119" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="202" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="121" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="122" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="203" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="125" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="126" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="204" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="130" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="131" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="205" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="134" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="206" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="136" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1666,44 +1654,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>profit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>new_cases</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>hospitalized</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rolling_profit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>sales_pct_change</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1711,10 +1699,10 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>36627.07</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="2" t="n">
         <v>1490.9</v>
       </c>
       <c r="E2" t="n">
@@ -1727,7 +1715,7 @@
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1735,10 +1723,10 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="3" t="n">
         <v>26120.18</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>1775.53</v>
       </c>
       <c r="E3" t="n">
@@ -1753,7 +1741,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1761,10 +1749,10 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>33591.53</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="6" t="n">
         <v>1297.55</v>
       </c>
       <c r="E4" t="n">
@@ -1781,7 +1769,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1789,10 +1777,10 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>24267.89</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>1186.19</v>
       </c>
       <c r="E5" t="n">
@@ -1809,7 +1797,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1817,10 +1805,10 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>30944.1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>1753.54</v>
       </c>
       <c r="E6" t="n">
@@ -1833,11 +1821,11 @@
         <v>1412.426666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2751046753549648</v>
+        <v>0.2751046753549649</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1845,10 +1833,10 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>29744.69</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>1097.35</v>
       </c>
       <c r="E7" t="n">
@@ -1861,11 +1849,11 @@
         <v>1345.693333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.038760539165786</v>
+        <v>-0.03876053916578603</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1873,10 +1861,10 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="13" t="n">
         <v>29612.16</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="14" t="n">
         <v>1639.93</v>
       </c>
       <c r="E8" t="n">
@@ -1889,11 +1877,11 @@
         <v>1496.94</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0044555851817584</v>
+        <v>-0.004455585181758481</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1901,10 +1889,10 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>31635.41</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <v>1505</v>
       </c>
       <c r="E9" t="n">
@@ -1917,11 +1905,11 @@
         <v>1414.093333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0683249719034342</v>
+        <v>0.06832497190343423</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1929,10 +1917,10 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="17" t="n">
         <v>29429.83</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <v>1651.17</v>
       </c>
       <c r="E10" t="n">
@@ -1945,11 +1933,11 @@
         <v>1598.7</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0697187107737816</v>
+        <v>-0.06971871077378167</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1957,10 +1945,10 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>29827.85</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <v>1568.44</v>
       </c>
       <c r="E11" t="n">
@@ -1973,11 +1961,11 @@
         <v>1574.87</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0135243730595793</v>
+        <v>0.01352437305957932</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1985,10 +1973,10 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="21" t="n">
         <v>34508.69</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>1673.68</v>
       </c>
       <c r="E12" t="n">
@@ -2005,7 +1993,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2013,10 +2001,10 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="23" t="n">
         <v>33967.86</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>1425.52</v>
       </c>
       <c r="E13" t="n">
@@ -2029,11 +2017,11 @@
         <v>1555.88</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0156722842854944</v>
+        <v>-0.0156722842854945</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2041,10 +2029,10 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="25" t="n">
         <v>31433.78</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="26" t="n">
         <v>1529.73</v>
       </c>
       <c r="E14" t="n">
@@ -2057,11 +2045,11 @@
         <v>1542.976666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0746022858078195</v>
+        <v>-0.07460228580781958</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2069,10 +2057,10 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="27" t="n">
         <v>28894.59</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="28" t="n">
         <v>1394.35</v>
       </c>
       <c r="E15" t="n">
@@ -2085,11 +2073,11 @@
         <v>1449.866666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0807790218039319</v>
+        <v>-0.08077902180393193</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2097,10 +2085,10 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="29" t="n">
         <v>28577.56</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="7" t="n">
         <v>1318.93</v>
       </c>
       <c r="E16" t="n">
@@ -2113,11 +2101,11 @@
         <v>1414.336666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0109719501124604</v>
+        <v>-0.01097195011246044</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2125,10 +2113,10 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="19" t="n">
         <v>29848.65</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>1185.45</v>
       </c>
       <c r="E17" t="n">
@@ -2141,11 +2129,11 @@
         <v>1299.576666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0444786048913903</v>
+        <v>0.04447860489139033</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2153,27 +2141,27 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="30" t="n">
         <v>30464.44</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="31" t="n">
         <v>1274.88</v>
       </c>
       <c r="E18" t="n">
         <v>15482</v>
       </c>
       <c r="F18" t="n">
-        <v>2562.290322580646</v>
+        <v>2562.290322580645</v>
       </c>
       <c r="G18" t="n">
         <v>1259.753333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0206304137708068</v>
+        <v>0.02063041377080688</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2181,10 +2169,10 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="C19" s="33" t="n">
+      <c r="C19" s="32" t="n">
         <v>31799.25</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="33" t="n">
         <v>1618.65</v>
       </c>
       <c r="E19" t="n">
@@ -2197,11 +2185,11 @@
         <v>1359.66</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0438153466796042</v>
+        <v>0.04381534667960429</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2209,10 +2197,10 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="34" t="n">
         <v>30297.26</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="3" t="n">
         <v>1488.22</v>
       </c>
       <c r="E20" t="n">
@@ -2225,11 +2213,11 @@
         <v>1460.583333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0472335039348412</v>
+        <v>-0.04723350393484127</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2237,10 +2225,10 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n">
+      <c r="C21" s="35" t="n">
         <v>29537.68</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="36" t="n">
         <v>1630.27</v>
       </c>
       <c r="E21" t="n">
@@ -2253,11 +2241,11 @@
         <v>1579.046666666666</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0250709140034445</v>
+        <v>-0.02507091400344452</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2265,10 +2253,10 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C22" s="30" t="n">
         <v>30471.41</v>
       </c>
-      <c r="D22" s="38" t="n">
+      <c r="D22" s="37" t="n">
         <v>889.96</v>
       </c>
       <c r="E22" t="n">
@@ -2281,11 +2269,11 @@
         <v>1336.15</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0316114874289381</v>
+        <v>0.03161148742893816</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2293,10 +2281,10 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="38" t="n">
         <v>32605.12</v>
       </c>
-      <c r="D23" s="40" t="n">
+      <c r="D23" s="39" t="n">
         <v>1831.13</v>
       </c>
       <c r="E23" t="n">
@@ -2309,11 +2297,11 @@
         <v>1450.453333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0700233431928485</v>
+        <v>0.07002334319284853</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2321,10 +2309,10 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="40" t="n">
         <v>34901.36</v>
       </c>
-      <c r="D24" s="40" t="n">
+      <c r="D24" s="39" t="n">
         <v>1830.56</v>
       </c>
       <c r="E24" t="n">
@@ -2337,11 +2325,11 @@
         <v>1517.216666666666</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0704257490848063</v>
+        <v>0.07042574908480637</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2349,10 +2337,10 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="C25" s="42" t="n">
+      <c r="C25" s="41" t="n">
         <v>30038.75</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>1183.79</v>
       </c>
       <c r="E25" t="n">
@@ -2365,11 +2353,11 @@
         <v>1615.16</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.13932437016781</v>
+        <v>-0.1393243701678101</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2377,10 +2365,10 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="C26" s="43" t="n">
+      <c r="C26" s="42" t="n">
         <v>34837.38</v>
       </c>
-      <c r="D26" s="44" t="n">
+      <c r="D26" s="43" t="n">
         <v>1224.93</v>
       </c>
       <c r="E26" t="n">
@@ -2397,7 +2385,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2405,10 +2393,10 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="C27" s="45" t="n">
+      <c r="C27" s="44" t="n">
         <v>25787.21</v>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="45" t="n">
         <v>1411.14</v>
       </c>
       <c r="E27" t="n">
@@ -2425,7 +2413,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2433,10 +2421,10 @@
           <t>2022-03</t>
         </is>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C28" s="46" t="n">
         <v>31508.24</v>
       </c>
-      <c r="D28" s="48" t="n">
+      <c r="D28" s="47" t="n">
         <v>1370.39</v>
       </c>
       <c r="E28" t="n">
@@ -2453,7 +2441,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2461,10 +2449,10 @@
           <t>2022-04</t>
         </is>
       </c>
-      <c r="C29" s="49" t="n">
+      <c r="C29" s="48" t="n">
         <v>34087.07</v>
       </c>
-      <c r="D29" s="50" t="n">
+      <c r="D29" s="49" t="n">
         <v>1657.94</v>
       </c>
       <c r="E29" t="n">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2489,10 +2477,10 @@
           <t>2022-05</t>
         </is>
       </c>
-      <c r="C30" s="51" t="n">
+      <c r="C30" s="50" t="n">
         <v>23871.13</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>1295.14</v>
       </c>
       <c r="E30" t="n">
@@ -2509,7 +2497,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2517,10 +2505,10 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="C31" s="52" t="n">
+      <c r="C31" s="51" t="n">
         <v>36234.2</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="33" t="n">
         <v>1619.16</v>
       </c>
       <c r="E31" t="n">
@@ -2537,7 +2525,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2545,10 +2533,10 @@
           <t>2022-07</t>
         </is>
       </c>
-      <c r="C32" s="53" t="n">
+      <c r="C32" s="52" t="n">
         <v>31283.22</v>
       </c>
-      <c r="D32" s="54" t="n">
+      <c r="D32" s="53" t="n">
         <v>1038.6</v>
       </c>
       <c r="E32" t="n">
@@ -2561,11 +2549,11 @@
         <v>1317.633333333333</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1366383140789639</v>
+        <v>-0.136638314078964</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2573,10 +2561,10 @@
           <t>2022-08</t>
         </is>
       </c>
-      <c r="C33" s="55" t="n">
+      <c r="C33" s="54" t="n">
         <v>27847.87</v>
       </c>
-      <c r="D33" s="56" t="n">
+      <c r="D33" s="55" t="n">
         <v>948.15</v>
       </c>
       <c r="E33" t="n">
@@ -2589,11 +2577,11 @@
         <v>1201.97</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1098144628334296</v>
+        <v>-0.1098144628334297</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2601,10 +2589,10 @@
           <t>2022-09</t>
         </is>
       </c>
-      <c r="C34" s="57" t="n">
+      <c r="C34" s="56" t="n">
         <v>30557.5</v>
       </c>
-      <c r="D34" s="58" t="n">
+      <c r="D34" s="57" t="n">
         <v>1910.41</v>
       </c>
       <c r="E34" t="n">
@@ -2617,11 +2605,11 @@
         <v>1299.053333333333</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0973011580418898</v>
+        <v>0.09730115804188988</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2629,10 +2617,10 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="C35" s="24" t="n">
+      <c r="C35" s="23" t="n">
         <v>33963.1</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="15" t="n">
         <v>1980.37</v>
       </c>
       <c r="E35" t="n">
@@ -2649,7 +2637,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2657,10 +2645,10 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="C36" s="59" t="n">
+      <c r="C36" s="58" t="n">
         <v>27383.74</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="2" t="n">
         <v>1493.79</v>
       </c>
       <c r="E36" t="n">
@@ -2677,7 +2665,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2685,10 +2673,10 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="C37" s="60" t="n">
+      <c r="C37" s="59" t="n">
         <v>31102.32</v>
       </c>
-      <c r="D37" s="61" t="n">
+      <c r="D37" s="60" t="n">
         <v>1287.05</v>
       </c>
       <c r="E37" t="n">
@@ -2705,7 +2693,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2713,10 +2701,10 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="C38" s="62" t="n">
+      <c r="C38" s="61" t="n">
         <v>32001.93</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="2" t="n">
         <v>1492.09</v>
       </c>
       <c r="E38" t="n">
@@ -2729,11 +2717,11 @@
         <v>1424.31</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0289242088693062</v>
+        <v>0.02892420886930624</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2741,10 +2729,10 @@
           <t>2023-02</t>
         </is>
       </c>
-      <c r="C39" s="63" t="n">
+      <c r="C39" s="62" t="n">
         <v>25549.9</v>
       </c>
-      <c r="D39" s="64" t="n">
+      <c r="D39" s="63" t="n">
         <v>921.45</v>
       </c>
       <c r="E39" t="n">
@@ -2761,7 +2749,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2769,10 +2757,10 @@
           <t>2023-03</t>
         </is>
       </c>
-      <c r="C40" s="65" t="n">
+      <c r="C40" s="64" t="n">
         <v>30641.34</v>
       </c>
-      <c r="D40" s="66" t="n">
+      <c r="D40" s="65" t="n">
         <v>1769.22</v>
       </c>
       <c r="E40" t="n">
@@ -2789,7 +2777,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2797,10 +2785,10 @@
           <t>2023-04</t>
         </is>
       </c>
-      <c r="C41" s="50" t="n">
+      <c r="C41" s="49" t="n">
         <v>28023.87</v>
       </c>
-      <c r="D41" s="67" t="n">
+      <c r="D41" s="66" t="n">
         <v>1138.85</v>
       </c>
       <c r="E41" t="n">
@@ -2813,11 +2801,11 @@
         <v>1276.506666666667</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.08542283072476591</v>
+        <v>-0.08542283072476597</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2825,10 +2813,10 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="C42" s="68" t="n">
+      <c r="C42" s="67" t="n">
         <v>32323.74</v>
       </c>
-      <c r="D42" s="69" t="n">
+      <c r="D42" s="68" t="n">
         <v>918.46</v>
       </c>
       <c r="E42" t="n">
@@ -2845,7 +2833,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2853,10 +2841,10 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="C43" s="70" t="n">
+      <c r="C43" s="69" t="n">
         <v>24514.78</v>
       </c>
-      <c r="D43" s="71" t="n">
+      <c r="D43" s="70" t="n">
         <v>1134.04</v>
       </c>
       <c r="E43" t="n">
@@ -2873,7 +2861,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2881,10 +2869,10 @@
           <t>2023-07</t>
         </is>
       </c>
-      <c r="C44" s="72" t="n">
+      <c r="C44" s="71" t="n">
         <v>36327.15</v>
       </c>
-      <c r="D44" s="73" t="n">
+      <c r="D44" s="72" t="n">
         <v>2050.43</v>
       </c>
       <c r="E44" t="n">
@@ -2901,7 +2889,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2909,10 +2897,10 @@
           <t>2023-08</t>
         </is>
       </c>
-      <c r="C45" s="24" t="n">
+      <c r="C45" s="23" t="n">
         <v>33966.11</v>
       </c>
-      <c r="D45" s="74" t="n">
+      <c r="D45" s="73" t="n">
         <v>2158.57</v>
       </c>
       <c r="E45" t="n">
@@ -2929,7 +2917,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2937,10 +2925,10 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="C46" s="75" t="n">
+      <c r="C46" s="74" t="n">
         <v>29217.39</v>
       </c>
-      <c r="D46" s="44" t="n">
+      <c r="D46" s="43" t="n">
         <v>1224.42</v>
       </c>
       <c r="E46" t="n">
@@ -2957,7 +2945,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2965,10 +2953,10 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="C47" s="76" t="n">
+      <c r="C47" s="75" t="n">
         <v>36429.74</v>
       </c>
-      <c r="D47" s="42" t="n">
+      <c r="D47" s="41" t="n">
         <v>1842.16</v>
       </c>
       <c r="E47" t="n">
@@ -2981,11 +2969,11 @@
         <v>1741.716666666667</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2468512759010985</v>
+        <v>0.2468512759010986</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2993,10 +2981,10 @@
           <t>2023-11</t>
         </is>
       </c>
-      <c r="C48" s="26" t="n">
+      <c r="C48" s="25" t="n">
         <v>31451.28</v>
       </c>
-      <c r="D48" s="53" t="n">
+      <c r="D48" s="52" t="n">
         <v>1942.05</v>
       </c>
       <c r="E48" t="n">
@@ -3013,7 +3001,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3021,11 +3009,11 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="4" t="n">
         <v>29356.68</v>
       </c>
-      <c r="D49" s="77" t="n">
-        <v>929.41</v>
+      <c r="D49" s="76" t="n">
+        <v>929.4100000000001</v>
       </c>
       <c r="E49" t="n">
         <v>15359</v>
@@ -3037,11 +3025,11 @@
         <v>1571.206666666667</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0665982433783298</v>
+        <v>-0.06659824337832987</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3049,10 +3037,10 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="C50" s="53" t="n">
+      <c r="C50" s="52" t="n">
         <v>31251.36</v>
       </c>
-      <c r="D50" s="78" t="n">
+      <c r="D50" s="77" t="n">
         <v>1103.3</v>
       </c>
       <c r="E50" t="n">
@@ -3069,7 +3057,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3077,10 +3065,10 @@
           <t>2024-02</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="28" t="n">
         <v>25047.65</v>
       </c>
-      <c r="D51" s="79" t="n">
+      <c r="D51" s="78" t="n">
         <v>1303.47</v>
       </c>
       <c r="E51" t="n">
@@ -3093,11 +3081,11 @@
         <v>1112.06</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1985100808412818</v>
+        <v>-0.1985100808412819</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3105,10 +3093,10 @@
           <t>2024-03</t>
         </is>
       </c>
-      <c r="C52" s="80" t="n">
+      <c r="C52" s="79" t="n">
         <v>26960.22</v>
       </c>
-      <c r="D52" s="7" t="n">
+      <c r="D52" s="6" t="n">
         <v>1302.29</v>
       </c>
       <c r="E52" t="n">
@@ -3118,14 +3106,14 @@
         <v>2367.548387096774</v>
       </c>
       <c r="G52" t="n">
-        <v>1236.353333333334</v>
+        <v>1236.353333333333</v>
       </c>
       <c r="H52" t="n">
-        <v>0.07635726305661419</v>
+        <v>0.07635726305661428</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3133,10 +3121,10 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="C53" s="81" t="n">
+      <c r="C53" s="80" t="n">
         <v>31923.34</v>
       </c>
-      <c r="D53" s="82" t="n">
+      <c r="D53" s="81" t="n">
         <v>1415.54</v>
       </c>
       <c r="E53" t="n">
@@ -3153,7 +3141,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3161,27 +3149,27 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="C54" s="73" t="n">
+      <c r="C54" s="72" t="n">
         <v>32431.44</v>
       </c>
-      <c r="D54" s="83" t="n">
+      <c r="D54" s="82" t="n">
         <v>1869.81</v>
       </c>
       <c r="E54" t="n">
         <v>15470</v>
       </c>
       <c r="F54" t="n">
-        <v>2805.709677419354</v>
+        <v>2805.709677419355</v>
       </c>
       <c r="G54" t="n">
         <v>1529.213333333333</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0159162543768915</v>
+        <v>0.01591625437689159</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3189,10 +3177,10 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="C55" s="75" t="n">
+      <c r="C55" s="74" t="n">
         <v>29230.18</v>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="12" t="n">
         <v>1094.47</v>
       </c>
       <c r="E55" t="n">
@@ -3209,7 +3197,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3217,10 +3205,10 @@
           <t>2024-07</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="4" t="n">
         <v>29417.74</v>
       </c>
-      <c r="D56" s="28" t="n">
+      <c r="D56" s="27" t="n">
         <v>1733.71</v>
       </c>
       <c r="E56" t="n">
@@ -3233,11 +3221,11 @@
         <v>1565.996666666667</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0064166556620588</v>
+        <v>0.006416655662058846</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3245,10 +3233,10 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="C57" s="47" t="n">
+      <c r="C57" s="46" t="n">
         <v>31507.89</v>
       </c>
-      <c r="D57" s="84" t="n">
+      <c r="D57" s="83" t="n">
         <v>2094.03</v>
       </c>
       <c r="E57" t="n">
@@ -3261,11 +3249,11 @@
         <v>1640.736666666667</v>
       </c>
       <c r="H57" t="n">
-        <v>0.07105066534682811</v>
+        <v>0.07105066534682813</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3273,10 +3261,10 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="C58" s="11" t="n">
+      <c r="C58" s="10" t="n">
         <v>29159.54</v>
       </c>
-      <c r="D58" s="45" t="n">
+      <c r="D58" s="44" t="n">
         <v>1453.11</v>
       </c>
       <c r="E58" t="n">
@@ -3289,11 +3277,11 @@
         <v>1760.283333333334</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.0745321251280234</v>
+        <v>-0.07453212512802343</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3301,10 +3289,10 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C59" s="85" t="n">
+      <c r="C59" s="84" t="n">
         <v>32265.38</v>
       </c>
-      <c r="D59" s="86" t="n">
+      <c r="D59" s="85" t="n">
         <v>1717.07</v>
       </c>
       <c r="E59" t="n">
@@ -3321,7 +3309,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3329,10 +3317,10 @@
           <t>2024-11</t>
         </is>
       </c>
-      <c r="C60" s="87" t="n">
+      <c r="C60" s="86" t="n">
         <v>32176.81</v>
       </c>
-      <c r="D60" s="88" t="n">
+      <c r="D60" s="87" t="n">
         <v>2083.05</v>
       </c>
       <c r="E60" t="n">
@@ -3345,11 +3333,11 @@
         <v>1751.076666666667</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.0027450474781328</v>
+        <v>-0.002745047478132867</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3357,10 +3345,10 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="C61" s="40" t="n">
+      <c r="C61" s="39" t="n">
         <v>29992.5</v>
       </c>
-      <c r="D61" s="89" t="n">
+      <c r="D61" s="88" t="n">
         <v>1538.15</v>
       </c>
       <c r="E61" t="n">
@@ -3373,11 +3361,11 @@
         <v>1779.423333333333</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0678846038497912</v>
+        <v>-0.06788460384979123</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3385,10 +3373,10 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="C62" s="22" t="n">
+      <c r="C62" s="21" t="n">
         <v>34502</v>
       </c>
-      <c r="D62" s="90" t="n">
+      <c r="D62" s="89" t="n">
         <v>2130.74</v>
       </c>
       <c r="E62" t="n">
@@ -3405,7 +3393,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3413,10 +3401,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="C63" s="91" t="n">
+      <c r="C63" s="90" t="n">
         <v>31610.23</v>
       </c>
-      <c r="D63" s="80" t="n">
+      <c r="D63" s="79" t="n">
         <v>1563.28</v>
       </c>
       <c r="E63" t="n">
@@ -3429,11 +3417,11 @@
         <v>1744.056666666667</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.0838145614746971</v>
+        <v>-0.08381456147469712</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3441,10 +3429,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="C64" s="92" t="n">
+      <c r="C64" s="91" t="n">
         <v>32482.17</v>
       </c>
-      <c r="D64" s="39" t="n">
+      <c r="D64" s="38" t="n">
         <v>2065.91</v>
       </c>
       <c r="E64" t="n">
@@ -3457,11 +3445,11 @@
         <v>1919.976666666667</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0275841080561576</v>
+        <v>0.02758410805615763</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3469,10 +3457,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="C65" s="93" t="n">
+      <c r="C65" s="92" t="n">
         <v>28331.11</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="3" t="n">
         <v>1483.5</v>
       </c>
       <c r="E65" t="n">
@@ -3485,11 +3473,11 @@
         <v>1704.23</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1277950333983227</v>
+        <v>-0.1277950333983228</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3497,10 +3485,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="C66" s="41" t="n">
+      <c r="C66" s="40" t="n">
         <v>34864.81</v>
       </c>
-      <c r="D66" s="94" t="n">
+      <c r="D66" s="93" t="n">
         <v>1067.44</v>
       </c>
       <c r="E66" t="n">
@@ -3513,11 +3501,11 @@
         <v>1538.950000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2306192733006224</v>
+        <v>0.2306192733006225</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3525,10 +3513,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="C67" s="95" t="n">
+      <c r="C67" s="94" t="n">
         <v>30700.81</v>
       </c>
-      <c r="D67" s="96" t="n">
+      <c r="D67" s="95" t="n">
         <v>2128.09</v>
       </c>
       <c r="E67" t="n">
@@ -3545,7 +3533,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3553,10 +3541,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="C68" s="97" t="n">
+      <c r="C68" s="96" t="n">
         <v>25986.23</v>
       </c>
-      <c r="D68" s="98" t="n">
+      <c r="D68" s="97" t="n">
         <v>1118.09</v>
       </c>
       <c r="E68" t="n">
@@ -3573,7 +3561,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3581,10 +3569,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="C69" s="12" t="n">
+      <c r="C69" s="11" t="n">
         <v>29723.98</v>
       </c>
-      <c r="D69" s="12" t="n">
+      <c r="D69" s="11" t="n">
         <v>1810</v>
       </c>
       <c r="E69" t="n">
@@ -3597,11 +3585,11 @@
         <v>1685.393333333334</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1438357930334641</v>
+        <v>0.1438357930334642</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3609,10 +3597,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="C70" s="99" t="n">
+      <c r="C70" s="98" t="n">
         <v>33529.19</v>
       </c>
-      <c r="D70" s="88" t="n">
+      <c r="D70" s="87" t="n">
         <v>2078.26</v>
       </c>
       <c r="E70" t="n">
@@ -3629,7 +3617,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3637,10 +3625,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="C71" s="43" t="n">
+      <c r="C71" s="42" t="n">
         <v>34807.75</v>
       </c>
-      <c r="D71" s="40" t="n">
+      <c r="D71" s="39" t="n">
         <v>1832.38</v>
       </c>
       <c r="E71" t="n">
@@ -3653,11 +3641,11 @@
         <v>1906.88</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0381327434393732</v>
+        <v>0.03813274343937323</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3665,10 +3653,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="C72" s="21" t="n">
+      <c r="C72" s="20" t="n">
         <v>27058.07</v>
       </c>
-      <c r="D72" s="94" t="n">
+      <c r="D72" s="93" t="n">
         <v>1066.42</v>
       </c>
       <c r="E72" t="n">
@@ -3685,7 +3673,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3693,10 +3681,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="C73" s="33" t="n">
+      <c r="C73" s="32" t="n">
         <v>31830.41</v>
       </c>
-      <c r="D73" s="28" t="n">
+      <c r="D73" s="27" t="n">
         <v>1735.32</v>
       </c>
       <c r="E73" t="n">
@@ -3713,7 +3701,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3721,10 +3709,10 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="C74" s="100" t="n">
+      <c r="C74" s="99" t="n">
         <v>31140.03</v>
       </c>
-      <c r="D74" s="101" t="n">
+      <c r="D74" s="100" t="n">
         <v>2017.92</v>
       </c>
       <c r="E74" t="n">
@@ -3737,11 +3725,11 @@
         <v>1606.553333333334</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.0216893216267085</v>
+        <v>-0.02168932162670856</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3749,10 +3737,10 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="C75" s="66" t="n">
+      <c r="C75" s="65" t="n">
         <v>29323.87</v>
       </c>
-      <c r="D75" s="17" t="n">
+      <c r="D75" s="16" t="n">
         <v>1504.34</v>
       </c>
       <c r="E75" t="n">
@@ -3765,11 +3753,11 @@
         <v>1752.526666666667</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.0583223587132061</v>
+        <v>-0.05832235871320612</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3777,10 +3765,10 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="C76" s="102" t="n">
+      <c r="C76" s="101" t="n">
         <v>29904.61</v>
       </c>
-      <c r="D76" s="103" t="n">
+      <c r="D76" s="102" t="n">
         <v>2115.42</v>
       </c>
       <c r="E76" t="n">
@@ -3793,11 +3781,11 @@
         <v>1879.226666666667</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0198043436967905</v>
+        <v>0.01980434369679052</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3805,10 +3793,10 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C77" s="89" t="n">
+      <c r="C77" s="88" t="n">
         <v>26718.18</v>
       </c>
-      <c r="D77" s="89" t="n">
+      <c r="D77" s="88" t="n">
         <v>1537.24</v>
       </c>
       <c r="E77" t="n">
@@ -3821,11 +3809,11 @@
         <v>1719.000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.1065531367906152</v>
+        <v>-0.1065531367906153</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3833,10 +3821,10 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="C78" s="18" t="n">
+      <c r="C78" s="17" t="n">
         <v>29484.64</v>
       </c>
-      <c r="D78" s="104" t="n">
+      <c r="D78" s="103" t="n">
         <v>1556.7</v>
       </c>
       <c r="E78" t="n">
@@ -3849,11 +3837,11 @@
         <v>1736.453333333334</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1035422322927683</v>
+        <v>0.1035422322927684</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3861,10 +3849,10 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="C79" s="105" t="n">
+      <c r="C79" s="104" t="n">
         <v>35169.18</v>
       </c>
-      <c r="D79" s="106" t="n">
+      <c r="D79" s="105" t="n">
         <v>2321.88</v>
       </c>
       <c r="E79" t="n">
@@ -3881,7 +3869,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3889,10 +3877,10 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C80" s="95" t="n">
+      <c r="C80" s="94" t="n">
         <v>30750.91</v>
       </c>
-      <c r="D80" s="94" t="n">
+      <c r="D80" s="93" t="n">
         <v>1069.41</v>
       </c>
       <c r="E80" t="n">
@@ -3909,7 +3897,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3917,17 +3905,17 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="C81" s="107" t="n">
+      <c r="C81" s="106" t="n">
         <v>34616.21</v>
       </c>
-      <c r="D81" s="73" t="n">
+      <c r="D81" s="72" t="n">
         <v>2045.84</v>
       </c>
       <c r="E81" t="n">
         <v>15569</v>
       </c>
       <c r="F81" t="n">
-        <v>2738.290322580646</v>
+        <v>2738.290322580645</v>
       </c>
       <c r="G81" t="n">
         <v>1812.376666666667</v>
@@ -3937,7 +3925,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3945,10 +3933,10 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="C82" s="90" t="n">
+      <c r="C82" s="89" t="n">
         <v>33342.87</v>
       </c>
-      <c r="D82" s="108" t="n">
+      <c r="D82" s="107" t="n">
         <v>1739.01</v>
       </c>
       <c r="E82" t="n">
@@ -3961,11 +3949,11 @@
         <v>1618.086666666667</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.0367845006717949</v>
+        <v>-0.03678450067179495</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3973,10 +3961,10 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="C83" s="51" t="n">
+      <c r="C83" s="50" t="n">
         <v>23887.95</v>
       </c>
-      <c r="D83" s="109" t="n">
+      <c r="D83" s="108" t="n">
         <v>1337.64</v>
       </c>
       <c r="E83" t="n">
@@ -3989,11 +3977,11 @@
         <v>1707.496666666667</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.2835664716324659</v>
+        <v>-0.283566471632466</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4001,10 +3989,10 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="C84" s="104" t="n">
+      <c r="C84" s="103" t="n">
         <v>26877.85</v>
       </c>
-      <c r="D84" s="86" t="n">
+      <c r="D84" s="85" t="n">
         <v>1718.41</v>
       </c>
       <c r="E84" t="n">
@@ -4017,11 +4005,11 @@
         <v>1598.353333333334</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1251635238687287</v>
+        <v>0.1251635238687288</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4029,27 +4017,27 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="C85" s="110" t="n">
+      <c r="C85" s="109" t="n">
         <v>25150.76</v>
       </c>
-      <c r="D85" s="64" t="n">
+      <c r="D85" s="63" t="n">
         <v>924.05</v>
       </c>
       <c r="E85" t="n">
         <v>15669</v>
       </c>
       <c r="F85" t="n">
-        <v>2621.709677419354</v>
+        <v>2621.709677419355</v>
       </c>
       <c r="G85" t="n">
         <v>1326.700000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.06425699972281999</v>
+        <v>-0.06425699972282006</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -4057,10 +4045,10 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="C86" s="43" t="n">
+      <c r="C86" s="42" t="n">
         <v>34803</v>
       </c>
-      <c r="D86" s="111" t="n">
+      <c r="D86" s="110" t="n">
         <v>1194.96</v>
       </c>
       <c r="E86" t="n">
@@ -4077,7 +4065,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -4085,10 +4073,10 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="C87" s="18" t="n">
+      <c r="C87" s="17" t="n">
         <v>29464.26</v>
       </c>
-      <c r="D87" s="79" t="n">
+      <c r="D87" s="78" t="n">
         <v>1305.7</v>
       </c>
       <c r="E87" t="n">
@@ -4105,7 +4093,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -4113,10 +4101,10 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C88" s="5" t="n">
         <v>33581.8</v>
       </c>
-      <c r="D88" s="60" t="n">
+      <c r="D88" s="59" t="n">
         <v>1929.56</v>
       </c>
       <c r="E88" t="n">
@@ -4129,11 +4117,11 @@
         <v>1476.74</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1397469340821728</v>
+        <v>0.1397469340821729</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -4141,10 +4129,10 @@
           <t>2027-04</t>
         </is>
       </c>
-      <c r="C89" s="100" t="n">
+      <c r="C89" s="99" t="n">
         <v>31145.23</v>
       </c>
-      <c r="D89" s="74" t="n">
+      <c r="D89" s="73" t="n">
         <v>2162.52</v>
       </c>
       <c r="E89" t="n">
@@ -4157,11 +4145,11 @@
         <v>1799.26</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.0725562655962457</v>
+        <v>-0.07255626559624573</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -4169,10 +4157,10 @@
           <t>2027-05</t>
         </is>
       </c>
-      <c r="C90" s="26" t="n">
+      <c r="C90" s="25" t="n">
         <v>31409.83</v>
       </c>
-      <c r="D90" s="112" t="n">
+      <c r="D90" s="111" t="n">
         <v>1590.39</v>
       </c>
       <c r="E90" t="n">
@@ -4185,11 +4173,11 @@
         <v>1894.156666666667</v>
       </c>
       <c r="H90" t="n">
-        <v>0.008495682966540999</v>
+        <v>0.008495682966541018</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -4197,10 +4185,10 @@
           <t>2027-06</t>
         </is>
       </c>
-      <c r="C91" s="112" t="n">
+      <c r="C91" s="111" t="n">
         <v>27255.04</v>
       </c>
-      <c r="D91" s="79" t="n">
+      <c r="D91" s="78" t="n">
         <v>1308.41</v>
       </c>
       <c r="E91" t="n">
@@ -4217,7 +4205,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -4225,10 +4213,10 @@
           <t>2027-07</t>
         </is>
       </c>
-      <c r="C92" s="92" t="n">
+      <c r="C92" s="91" t="n">
         <v>32540.11</v>
       </c>
-      <c r="D92" s="113" t="n">
+      <c r="D92" s="112" t="n">
         <v>2357.54</v>
       </c>
       <c r="E92" t="n">
@@ -4241,11 +4229,11 @@
         <v>1752.113333333334</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1939116581740478</v>
+        <v>0.1939116581740479</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -4253,10 +4241,10 @@
           <t>2027-08</t>
         </is>
       </c>
-      <c r="C93" s="114" t="n">
+      <c r="C93" s="113" t="n">
         <v>33771.07</v>
       </c>
-      <c r="D93" s="42" t="n">
+      <c r="D93" s="41" t="n">
         <v>1837.17</v>
       </c>
       <c r="E93" t="n">
@@ -4269,11 +4257,11 @@
         <v>1834.373333333334</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0378290054950642</v>
+        <v>0.03782900549506429</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -4281,10 +4269,10 @@
           <t>2027-09</t>
         </is>
       </c>
-      <c r="C94" s="84" t="n">
+      <c r="C94" s="83" t="n">
         <v>32937.1</v>
       </c>
-      <c r="D94" s="115" t="n">
+      <c r="D94" s="114" t="n">
         <v>2638.83</v>
       </c>
       <c r="E94" t="n">
@@ -4293,15 +4281,15 @@
       <c r="F94" t="n">
         <v>2345.066666666667</v>
       </c>
-      <c r="G94" s="116" t="n">
+      <c r="G94" s="115" t="n">
         <v>2277.846666666667</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.0246948053467065</v>
+        <v>-0.02469480534670654</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -4309,10 +4297,10 @@
           <t>2027-10</t>
         </is>
       </c>
-      <c r="C95" s="47" t="n">
+      <c r="C95" s="46" t="n">
         <v>31478.74</v>
       </c>
-      <c r="D95" s="79" t="n">
+      <c r="D95" s="78" t="n">
         <v>1303.67</v>
       </c>
       <c r="E95" t="n">
@@ -4325,11 +4313,11 @@
         <v>1926.556666666667</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.0442771221510089</v>
+        <v>-0.04427712215100899</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -4337,10 +4325,10 @@
           <t>2027-11</t>
         </is>
       </c>
-      <c r="C96" s="34" t="n">
+      <c r="C96" s="33" t="n">
         <v>27588.89</v>
       </c>
-      <c r="D96" s="63" t="n">
+      <c r="D96" s="62" t="n">
         <v>1444.58</v>
       </c>
       <c r="E96" t="n">
@@ -4357,7 +4345,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -4365,10 +4353,10 @@
           <t>2027-12</t>
         </is>
       </c>
-      <c r="C97" s="93" t="n">
+      <c r="C97" s="92" t="n">
         <v>28394.8</v>
       </c>
-      <c r="D97" s="117" t="n">
+      <c r="D97" s="116" t="n">
         <v>982.49</v>
       </c>
       <c r="E97" t="n">
@@ -4381,11 +4369,11 @@
         <v>1243.580000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0292113963265647</v>
+        <v>0.02921139632656478</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -4393,17 +4381,17 @@
           <t>2028-01</t>
         </is>
       </c>
-      <c r="C98" s="118" t="n">
+      <c r="C98" s="117" t="n">
         <v>31755.07</v>
       </c>
-      <c r="D98" s="119" t="n">
+      <c r="D98" s="118" t="n">
         <v>1665.12</v>
       </c>
       <c r="E98" t="n">
         <v>15535</v>
       </c>
       <c r="F98" t="n">
-        <v>2182.709677419354</v>
+        <v>2182.709677419355</v>
       </c>
       <c r="G98" t="n">
         <v>1364.063333333334</v>
@@ -4413,7 +4401,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -4421,10 +4409,10 @@
           <t>2028-02</t>
         </is>
       </c>
-      <c r="C99" s="11" t="n">
+      <c r="C99" s="10" t="n">
         <v>29096.46</v>
       </c>
-      <c r="D99" s="120" t="n">
+      <c r="D99" s="119" t="n">
         <v>1518.17</v>
       </c>
       <c r="E99" t="n">
@@ -4434,14 +4422,14 @@
         <v>2506</v>
       </c>
       <c r="G99" t="n">
-        <v>1388.593333333334</v>
+        <v>1388.593333333333</v>
       </c>
       <c r="H99" t="n">
         <v>-0.083722378820138</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -4449,27 +4437,27 @@
           <t>2028-03</t>
         </is>
       </c>
-      <c r="C100" s="121" t="n">
+      <c r="C100" s="120" t="n">
         <v>28819.27</v>
       </c>
-      <c r="D100" s="80" t="n">
+      <c r="D100" s="79" t="n">
         <v>1563.18</v>
       </c>
       <c r="E100" t="n">
         <v>15688</v>
       </c>
       <c r="F100" t="n">
-        <v>2255.290322580646</v>
+        <v>2255.290322580645</v>
       </c>
       <c r="G100" t="n">
         <v>1582.156666666667</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.0095265884578398</v>
+        <v>-0.009526588457839824</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -4477,10 +4465,10 @@
           <t>2028-04</t>
         </is>
       </c>
-      <c r="C101" s="118" t="n">
+      <c r="C101" s="117" t="n">
         <v>31730.54</v>
       </c>
-      <c r="D101" s="122" t="n">
+      <c r="D101" s="121" t="n">
         <v>1925.22</v>
       </c>
       <c r="E101" t="n">
@@ -4497,7 +4485,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -4505,10 +4493,10 @@
           <t>2028-05</t>
         </is>
       </c>
-      <c r="C102" s="20" t="n">
+      <c r="C102" s="19" t="n">
         <v>29788.32</v>
       </c>
-      <c r="D102" s="123" t="n">
+      <c r="D102" s="122" t="n">
         <v>1079.71</v>
       </c>
       <c r="E102" t="n">
@@ -4521,11 +4509,11 @@
         <v>1522.703333333334</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.0612097997701899</v>
+        <v>-0.06120979977018992</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -4533,10 +4521,10 @@
           <t>2028-06</t>
         </is>
       </c>
-      <c r="C103" s="86" t="n">
+      <c r="C103" s="85" t="n">
         <v>28679.29</v>
       </c>
-      <c r="D103" s="124" t="n">
+      <c r="D103" s="123" t="n">
         <v>772.41</v>
       </c>
       <c r="E103" t="n">
@@ -4549,11 +4537,11 @@
         <v>1259.113333333334</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.0372303641158682</v>
+        <v>-0.03723036411586822</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -4561,27 +4549,27 @@
           <t>2028-07</t>
         </is>
       </c>
-      <c r="C104" s="65" t="n">
+      <c r="C104" s="64" t="n">
         <v>30688.76</v>
       </c>
-      <c r="D104" s="109" t="n">
+      <c r="D104" s="108" t="n">
         <v>1334.79</v>
       </c>
       <c r="E104" t="n">
         <v>15341</v>
       </c>
       <c r="F104" t="n">
-        <v>2565.709677419354</v>
+        <v>2565.709677419355</v>
       </c>
       <c r="G104" t="n">
         <v>1062.303333333334</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0700669368035262</v>
+        <v>0.07006693680352627</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -4589,10 +4577,10 @@
           <t>2028-08</t>
         </is>
       </c>
-      <c r="C105" s="47" t="n">
+      <c r="C105" s="46" t="n">
         <v>31459.3</v>
       </c>
-      <c r="D105" s="125" t="n">
+      <c r="D105" s="124" t="n">
         <v>1526.63</v>
       </c>
       <c r="E105" t="n">
@@ -4605,11 +4593,11 @@
         <v>1211.276666666667</v>
       </c>
       <c r="H105" t="n">
-        <v>0.0251082155160389</v>
+        <v>0.02510821551603892</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -4617,10 +4605,10 @@
           <t>2028-09</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
+      <c r="C106" s="11" t="n">
         <v>29727.02</v>
       </c>
-      <c r="D106" s="46" t="n">
+      <c r="D106" s="45" t="n">
         <v>1414.86</v>
       </c>
       <c r="E106" t="n">
@@ -4633,11 +4621,11 @@
         <v>1425.426666666667</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.0550641622668018</v>
+        <v>-0.05506416226680189</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -4645,10 +4633,10 @@
           <t>2028-10</t>
         </is>
       </c>
-      <c r="C107" s="30" t="n">
+      <c r="C107" s="29" t="n">
         <v>28576.43</v>
       </c>
-      <c r="D107" s="86" t="n">
+      <c r="D107" s="85" t="n">
         <v>1720.17</v>
       </c>
       <c r="E107" t="n">
@@ -4665,7 +4653,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4673,10 +4661,10 @@
           <t>2028-11</t>
         </is>
       </c>
-      <c r="C108" s="126" t="n">
+      <c r="C108" s="125" t="n">
         <v>34927.34</v>
       </c>
-      <c r="D108" s="127" t="n">
+      <c r="D108" s="126" t="n">
         <v>1707.9</v>
       </c>
       <c r="E108" t="n">
@@ -4693,7 +4681,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4701,10 +4689,10 @@
           <t>2028-12</t>
         </is>
       </c>
-      <c r="C109" s="128" t="n">
+      <c r="C109" s="127" t="n">
         <v>35260.67</v>
       </c>
-      <c r="D109" s="4" t="n">
+      <c r="D109" s="3" t="n">
         <v>1486.85</v>
       </c>
       <c r="E109" t="n">
@@ -4717,11 +4705,11 @@
         <v>1638.306666666667</v>
       </c>
       <c r="H109" t="n">
-        <v>0.0095435266470336</v>
+        <v>0.009543526647033618</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4729,10 +4717,10 @@
           <t>2029-01</t>
         </is>
       </c>
-      <c r="C110" s="129" t="n">
+      <c r="C110" s="128" t="n">
         <v>33898.22</v>
       </c>
-      <c r="D110" s="62" t="n">
+      <c r="D110" s="61" t="n">
         <v>2013.6</v>
       </c>
       <c r="E110" t="n">
@@ -4745,11 +4733,11 @@
         <v>1736.116666666667</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.038639367884955</v>
+        <v>-0.03863936788495503</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4757,10 +4745,10 @@
           <t>2029-02</t>
         </is>
       </c>
-      <c r="C111" s="28" t="n">
+      <c r="C111" s="27" t="n">
         <v>28854.54</v>
       </c>
-      <c r="D111" s="130" t="n">
+      <c r="D111" s="129" t="n">
         <v>1090.5</v>
       </c>
       <c r="E111" t="n">
@@ -4777,7 +4765,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4785,10 +4773,10 @@
           <t>2029-03</t>
         </is>
       </c>
-      <c r="C112" s="131" t="n">
+      <c r="C112" s="130" t="n">
         <v>27416.62</v>
       </c>
-      <c r="D112" s="132" t="n">
+      <c r="D112" s="131" t="n">
         <v>880.9</v>
       </c>
       <c r="E112" t="n">
@@ -4801,11 +4789,11 @@
         <v>1328.333333333334</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.0498334057656092</v>
+        <v>-0.04983340576560924</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4813,10 +4801,10 @@
           <t>2029-04</t>
         </is>
       </c>
-      <c r="C113" s="68" t="n">
+      <c r="C113" s="67" t="n">
         <v>32341.49</v>
       </c>
-      <c r="D113" s="133" t="n">
+      <c r="D113" s="132" t="n">
         <v>1445.47</v>
       </c>
       <c r="E113" t="n">
@@ -4833,7 +4821,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4841,10 +4829,10 @@
           <t>2029-05</t>
         </is>
       </c>
-      <c r="C114" s="134" t="n">
+      <c r="C114" s="133" t="n">
         <v>24635.82</v>
       </c>
-      <c r="D114" s="67" t="n">
+      <c r="D114" s="66" t="n">
         <v>1142.37</v>
       </c>
       <c r="E114" t="n">
@@ -4857,11 +4845,11 @@
         <v>1156.246666666667</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.2382595854427238</v>
+        <v>-0.2382595854427239</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4869,10 +4857,10 @@
           <t>2029-06</t>
         </is>
       </c>
-      <c r="C115" s="97" t="n">
+      <c r="C115" s="96" t="n">
         <v>25972.24</v>
       </c>
-      <c r="D115" s="51" t="n">
+      <c r="D115" s="50" t="n">
         <v>1287.7</v>
       </c>
       <c r="E115" t="n">
@@ -4885,11 +4873,11 @@
         <v>1291.846666666667</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0542470272960267</v>
+        <v>0.05424702729602671</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4897,10 +4885,10 @@
           <t>2029-07</t>
         </is>
       </c>
-      <c r="C116" s="108" t="n">
+      <c r="C116" s="107" t="n">
         <v>29003.32</v>
       </c>
-      <c r="D116" s="46" t="n">
+      <c r="D116" s="45" t="n">
         <v>1413.29</v>
       </c>
       <c r="E116" t="n">
@@ -4913,11 +4901,11 @@
         <v>1281.120000000001</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1167046046086128</v>
+        <v>0.1167046046086129</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4925,10 +4913,10 @@
           <t>2029-08</t>
         </is>
       </c>
-      <c r="C117" s="135" t="n">
+      <c r="C117" s="134" t="n">
         <v>37555.77</v>
       </c>
-      <c r="D117" s="129" t="n">
+      <c r="D117" s="128" t="n">
         <v>2178.31</v>
       </c>
       <c r="E117" t="n">
@@ -4941,11 +4929,11 @@
         <v>1626.433333333334</v>
       </c>
       <c r="H117" t="n">
-        <v>0.2948783104830756</v>
+        <v>0.2948783104830757</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4953,10 +4941,10 @@
           <t>2029-09</t>
         </is>
       </c>
-      <c r="C118" s="11" t="n">
+      <c r="C118" s="10" t="n">
         <v>29089.84</v>
       </c>
-      <c r="D118" s="122" t="n">
+      <c r="D118" s="121" t="n">
         <v>1924.12</v>
       </c>
       <c r="E118" t="n">
@@ -4966,14 +4954,14 @@
         <v>2263.833333333333</v>
       </c>
       <c r="G118" t="n">
-        <v>1838.573333333333</v>
+        <v>1838.573333333334</v>
       </c>
       <c r="H118" t="n">
         <v>-0.2254228844196244</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4981,10 +4969,10 @@
           <t>2029-10</t>
         </is>
       </c>
-      <c r="C119" s="35" t="n">
+      <c r="C119" s="34" t="n">
         <v>30319.14</v>
       </c>
-      <c r="D119" s="82" t="n">
+      <c r="D119" s="81" t="n">
         <v>1419.52</v>
       </c>
       <c r="E119" t="n">
@@ -4994,14 +4982,14 @@
         <v>2430.16129032258</v>
       </c>
       <c r="G119" t="n">
-        <v>1840.65</v>
+        <v>1840.650000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0422587405087135</v>
+        <v>0.04225874050871359</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -5009,10 +4997,10 @@
           <t>2029-11</t>
         </is>
       </c>
-      <c r="C120" s="65" t="n">
+      <c r="C120" s="64" t="n">
         <v>30695.71</v>
       </c>
-      <c r="D120" s="136" t="n">
+      <c r="D120" s="135" t="n">
         <v>2087.46</v>
       </c>
       <c r="E120" t="n">
@@ -5022,14 +5010,14 @@
         <v>2531.6</v>
       </c>
       <c r="G120" t="n">
-        <v>1810.366666666668</v>
+        <v>1810.366666666667</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0124202071694645</v>
+        <v>0.01242020716946457</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -5037,10 +5025,10 @@
           <t>2029-12</t>
         </is>
       </c>
-      <c r="C121" s="26" t="n">
+      <c r="C121" s="25" t="n">
         <v>31402.09</v>
       </c>
-      <c r="D121" s="137" t="n">
+      <c r="D121" s="136" t="n">
         <v>1473.76</v>
       </c>
       <c r="E121" t="n">
@@ -5053,11 +5041,11 @@
         <v>1660.246666666667</v>
       </c>
       <c r="H121" t="n">
-        <v>0.0230123362515479</v>
+        <v>0.02301233625154797</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -5065,10 +5053,10 @@
           <t>2030-01</t>
         </is>
       </c>
-      <c r="C122" s="50" t="n">
+      <c r="C122" s="49" t="n">
         <v>28073.36</v>
       </c>
-      <c r="D122" s="138" t="n">
+      <c r="D122" s="137" t="n">
         <v>995.89</v>
       </c>
       <c r="E122" t="n">
@@ -5081,11 +5069,11 @@
         <v>1519.036666666667</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.1060034539102333</v>
+        <v>-0.1060034539102334</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -5093,10 +5081,10 @@
           <t>2030-02</t>
         </is>
       </c>
-      <c r="C123" s="139" t="n">
+      <c r="C123" s="138" t="n">
         <v>26765.4</v>
       </c>
-      <c r="D123" s="140" t="n">
+      <c r="D123" s="139" t="n">
         <v>1070.95</v>
       </c>
       <c r="E123" t="n">
@@ -5109,11 +5097,11 @@
         <v>1180.200000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.0465907892749567</v>
+        <v>-0.04659078927495675</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -5121,10 +5109,10 @@
           <t>2030-03</t>
         </is>
       </c>
-      <c r="C124" s="99" t="n">
+      <c r="C124" s="98" t="n">
         <v>33535.08</v>
       </c>
-      <c r="D124" s="141" t="n">
+      <c r="D124" s="140" t="n">
         <v>2111.13</v>
       </c>
       <c r="E124" t="n">
@@ -5141,7 +5129,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -5149,10 +5137,10 @@
           <t>2030-04</t>
         </is>
       </c>
-      <c r="C125" s="100" t="n">
+      <c r="C125" s="99" t="n">
         <v>31160</v>
       </c>
-      <c r="D125" s="142" t="n">
+      <c r="D125" s="141" t="n">
         <v>1144.91</v>
       </c>
       <c r="E125" t="n">
@@ -5165,11 +5153,11 @@
         <v>1442.330000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.0708237463575456</v>
+        <v>-0.07082374635754562</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -5177,10 +5165,10 @@
           <t>2030-05</t>
         </is>
       </c>
-      <c r="C126" s="143" t="n">
+      <c r="C126" s="142" t="n">
         <v>32996.91</v>
       </c>
-      <c r="D126" s="80" t="n">
+      <c r="D126" s="79" t="n">
         <v>1563.16</v>
       </c>
       <c r="E126" t="n">
@@ -5193,11 +5181,11 @@
         <v>1606.400000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>0.0589508985879332</v>
+        <v>0.05895089858793323</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -5205,27 +5193,27 @@
           <t>2030-06</t>
         </is>
       </c>
-      <c r="C127" s="63" t="n">
+      <c r="C127" s="62" t="n">
         <v>25539.9</v>
       </c>
-      <c r="D127" s="29" t="n">
+      <c r="D127" s="28" t="n">
         <v>1395.16</v>
       </c>
       <c r="E127" t="n">
         <v>15024</v>
       </c>
       <c r="F127" t="n">
-        <v>1949.566666666666</v>
+        <v>1949.566666666667</v>
       </c>
       <c r="G127" t="n">
         <v>1367.743333333334</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.2259911609905289</v>
+        <v>-0.225991160990529</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -5233,10 +5221,10 @@
           <t>2030-07</t>
         </is>
       </c>
-      <c r="C128" s="36" t="n">
+      <c r="C128" s="35" t="n">
         <v>29562.48</v>
       </c>
-      <c r="D128" s="17" t="n">
+      <c r="D128" s="16" t="n">
         <v>1504.53</v>
       </c>
       <c r="E128" t="n">
@@ -5246,14 +5234,14 @@
         <v>2600.129032258064</v>
       </c>
       <c r="G128" t="n">
-        <v>1487.616666666668</v>
+        <v>1487.616666666667</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1575017913147662</v>
+        <v>0.1575017913147663</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -5261,10 +5249,10 @@
           <t>2030-08</t>
         </is>
       </c>
-      <c r="C129" s="34" t="n">
+      <c r="C129" s="33" t="n">
         <v>27638.66</v>
       </c>
-      <c r="D129" s="119" t="n">
+      <c r="D129" s="118" t="n">
         <v>1663.81</v>
       </c>
       <c r="E129" t="n">
@@ -5277,11 +5265,11 @@
         <v>1521.166666666667</v>
       </c>
       <c r="H129" t="n">
-        <v>-0.0650764076626859</v>
+        <v>-0.06507640766268596</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -5289,10 +5277,10 @@
           <t>2030-09</t>
         </is>
       </c>
-      <c r="C130" s="144" t="n">
+      <c r="C130" s="143" t="n">
         <v>30139.48</v>
       </c>
-      <c r="D130" s="82" t="n">
+      <c r="D130" s="81" t="n">
         <v>1417.94</v>
       </c>
       <c r="E130" t="n">
@@ -5305,11 +5293,11 @@
         <v>1528.760000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>0.0904826789721353</v>
+        <v>0.09048267897213536</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -5317,10 +5305,10 @@
           <t>2030-10</t>
         </is>
       </c>
-      <c r="C131" s="55" t="n">
+      <c r="C131" s="54" t="n">
         <v>27840.04</v>
       </c>
-      <c r="D131" s="145" t="n">
+      <c r="D131" s="144" t="n">
         <v>1252.71</v>
       </c>
       <c r="E131" t="n">
@@ -5337,7 +5325,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -5345,10 +5333,10 @@
           <t>2030-11</t>
         </is>
       </c>
-      <c r="C132" s="58" t="n">
+      <c r="C132" s="57" t="n">
         <v>30834.93</v>
       </c>
-      <c r="D132" s="109" t="n">
+      <c r="D132" s="108" t="n">
         <v>1335.39</v>
       </c>
       <c r="E132" t="n">
@@ -5365,7 +5353,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -5373,10 +5361,10 @@
           <t>2030-12</t>
         </is>
       </c>
-      <c r="C133" s="60" t="n">
+      <c r="C133" s="59" t="n">
         <v>31074.33</v>
       </c>
-      <c r="D133" s="146" t="n">
+      <c r="D133" s="145" t="n">
         <v>1157.55</v>
       </c>
       <c r="E133" t="n">
@@ -5389,11 +5377,11 @@
         <v>1248.550000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>0.0077639222790517</v>
+        <v>0.00776392227905176</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -5401,10 +5389,10 @@
           <t>2031-01</t>
         </is>
       </c>
-      <c r="C134" s="42" t="n">
+      <c r="C134" s="41" t="n">
         <v>30072.47</v>
       </c>
-      <c r="D134" s="144" t="n">
+      <c r="D134" s="143" t="n">
         <v>1849.73</v>
       </c>
       <c r="E134" t="n">
@@ -5417,11 +5405,11 @@
         <v>1447.556666666667</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.0322407594950558</v>
+        <v>-0.03224075949505589</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -5429,10 +5417,10 @@
           <t>2031-02</t>
         </is>
       </c>
-      <c r="C135" s="22" t="n">
+      <c r="C135" s="21" t="n">
         <v>34527.89</v>
       </c>
-      <c r="D135" s="147" t="n">
+      <c r="D135" s="146" t="n">
         <v>2075.13</v>
       </c>
       <c r="E135" t="n">
@@ -5449,7 +5437,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -5457,10 +5445,10 @@
           <t>2031-03</t>
         </is>
       </c>
-      <c r="C136" s="88" t="n">
+      <c r="C136" s="87" t="n">
         <v>32757.94</v>
       </c>
-      <c r="D136" s="83" t="n">
+      <c r="D136" s="82" t="n">
         <v>1868.55</v>
       </c>
       <c r="E136" t="n">
@@ -5477,7 +5465,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -5485,10 +5473,10 @@
           <t>2031-04</t>
         </is>
       </c>
-      <c r="C137" s="22" t="n">
+      <c r="C137" s="21" t="n">
         <v>34569.77</v>
       </c>
-      <c r="D137" s="104" t="n">
+      <c r="D137" s="103" t="n">
         <v>1552.04</v>
       </c>
       <c r="E137" t="n">
@@ -5501,11 +5489,11 @@
         <v>1831.906666666667</v>
       </c>
       <c r="H137" t="n">
-        <v>0.0553096440130238</v>
+        <v>0.05530964401302385</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -5513,10 +5501,10 @@
           <t>2031-05</t>
         </is>
       </c>
-      <c r="C138" s="24" t="n">
+      <c r="C138" s="23" t="n">
         <v>33957.54</v>
       </c>
-      <c r="D138" s="118" t="n">
+      <c r="D138" s="117" t="n">
         <v>1992.56</v>
       </c>
       <c r="E138" t="n">
@@ -5529,11 +5517,11 @@
         <v>1804.383333333334</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.0177099818714442</v>
+        <v>-0.01770998187144424</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5541,10 +5529,10 @@
           <t>2031-06</t>
         </is>
       </c>
-      <c r="C139" s="67" t="n">
+      <c r="C139" s="66" t="n">
         <v>22177.22</v>
       </c>
-      <c r="D139" s="148" t="n">
+      <c r="D139" s="147" t="n">
         <v>751.29</v>
       </c>
       <c r="E139" t="n">
@@ -5557,11 +5545,11 @@
         <v>1431.963333333334</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.3469132334085448</v>
+        <v>-0.3469132334085449</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -5569,10 +5557,10 @@
           <t>2031-07</t>
         </is>
       </c>
-      <c r="C140" s="21" t="n">
+      <c r="C140" s="20" t="n">
         <v>27036.04</v>
       </c>
-      <c r="D140" s="133" t="n">
+      <c r="D140" s="132" t="n">
         <v>1450.9</v>
       </c>
       <c r="E140" t="n">
@@ -5589,7 +5577,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -5597,10 +5585,10 @@
           <t>2031-08</t>
         </is>
       </c>
-      <c r="C141" s="92" t="n">
+      <c r="C141" s="91" t="n">
         <v>32536.24</v>
       </c>
-      <c r="D141" s="23" t="n">
+      <c r="D141" s="22" t="n">
         <v>1671.43</v>
       </c>
       <c r="E141" t="n">
@@ -5613,11 +5601,11 @@
         <v>1291.206666666667</v>
       </c>
       <c r="H141" t="n">
-        <v>0.2034395569765394</v>
+        <v>0.2034395569765395</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -5625,10 +5613,10 @@
           <t>2031-09</t>
         </is>
       </c>
-      <c r="C142" s="95" t="n">
+      <c r="C142" s="94" t="n">
         <v>30763.09</v>
       </c>
-      <c r="D142" s="5" t="n">
+      <c r="D142" s="4" t="n">
         <v>1776.09</v>
       </c>
       <c r="E142" t="n">
@@ -5641,11 +5629,11 @@
         <v>1632.806666666667</v>
       </c>
       <c r="H142" t="n">
-        <v>-0.0544976924192839</v>
+        <v>-0.05449769241928393</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -5653,10 +5641,10 @@
           <t>2031-10</t>
         </is>
       </c>
-      <c r="C143" s="66" t="n">
+      <c r="C143" s="65" t="n">
         <v>29336.83</v>
       </c>
-      <c r="D143" s="109" t="n">
+      <c r="D143" s="108" t="n">
         <v>1336.08</v>
       </c>
       <c r="E143" t="n">
@@ -5669,11 +5657,11 @@
         <v>1594.533333333334</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.0463627028364185</v>
+        <v>-0.04636270283641852</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5681,10 +5669,10 @@
           <t>2031-11</t>
         </is>
       </c>
-      <c r="C144" s="58" t="n">
+      <c r="C144" s="57" t="n">
         <v>30815.61</v>
       </c>
-      <c r="D144" s="25" t="n">
+      <c r="D144" s="24" t="n">
         <v>1428.42</v>
       </c>
       <c r="E144" t="n">
@@ -5697,11 +5685,11 @@
         <v>1513.530000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0504069458083915</v>
+        <v>0.05040694580839156</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5709,10 +5697,10 @@
           <t>2031-12</t>
         </is>
       </c>
-      <c r="C145" s="57" t="n">
+      <c r="C145" s="56" t="n">
         <v>30562.18</v>
       </c>
-      <c r="D145" s="130" t="n">
+      <c r="D145" s="129" t="n">
         <v>1088.29</v>
       </c>
       <c r="E145" t="n">
@@ -5725,11 +5713,11 @@
         <v>1284.263333333334</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.0082240786406629</v>
+        <v>-0.008224078640662991</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -5737,10 +5725,10 @@
           <t>2032-01</t>
         </is>
       </c>
-      <c r="C146" s="114" t="n">
+      <c r="C146" s="113" t="n">
         <v>33802.34</v>
       </c>
-      <c r="D146" s="97" t="n">
+      <c r="D146" s="96" t="n">
         <v>1477.75</v>
       </c>
       <c r="E146" t="n">
@@ -5757,7 +5745,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -5765,10 +5753,10 @@
           <t>2032-02</t>
         </is>
       </c>
-      <c r="C147" s="18" t="n">
+      <c r="C147" s="17" t="n">
         <v>29470.66</v>
       </c>
-      <c r="D147" s="149" t="n">
+      <c r="D147" s="148" t="n">
         <v>1024.17</v>
       </c>
       <c r="E147" t="n">
@@ -5785,7 +5773,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -5793,27 +5781,27 @@
           <t>2032-03</t>
         </is>
       </c>
-      <c r="C148" s="122" t="n">
+      <c r="C148" s="121" t="n">
         <v>30949.46</v>
       </c>
-      <c r="D148" s="32" t="n">
+      <c r="D148" s="31" t="n">
         <v>1275.72</v>
       </c>
       <c r="E148" t="n">
         <v>15492</v>
       </c>
       <c r="F148" t="n">
-        <v>2841.290322580646</v>
+        <v>2841.290322580645</v>
       </c>
       <c r="G148" t="n">
         <v>1259.213333333334</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0501787201236754</v>
+        <v>0.05017872012367541</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -5821,10 +5809,10 @@
           <t>2032-04</t>
         </is>
       </c>
-      <c r="C149" s="150" t="n">
+      <c r="C149" s="149" t="n">
         <v>23364.97</v>
       </c>
-      <c r="D149" s="67" t="n">
+      <c r="D149" s="66" t="n">
         <v>1143.61</v>
       </c>
       <c r="E149" t="n">
@@ -5841,7 +5829,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -5849,10 +5837,10 @@
           <t>2032-05</t>
         </is>
       </c>
-      <c r="C150" s="33" t="n">
+      <c r="C150" s="32" t="n">
         <v>31871.62</v>
       </c>
-      <c r="D150" s="137" t="n">
+      <c r="D150" s="136" t="n">
         <v>1469.4</v>
       </c>
       <c r="E150" t="n">
@@ -5869,7 +5857,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -5877,10 +5865,10 @@
           <t>2032-06</t>
         </is>
       </c>
-      <c r="C151" s="74" t="n">
+      <c r="C151" s="73" t="n">
         <v>33664.45</v>
       </c>
-      <c r="D151" s="151" t="n">
+      <c r="D151" s="150" t="n">
         <v>1209.95</v>
       </c>
       <c r="E151" t="n">
@@ -5893,11 +5881,11 @@
         <v>1274.320000000001</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0562516119356342</v>
+        <v>0.05625161193563422</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -5905,27 +5893,27 @@
           <t>2032-07</t>
         </is>
       </c>
-      <c r="C152" s="102" t="n">
+      <c r="C152" s="101" t="n">
         <v>29895.65</v>
       </c>
-      <c r="D152" s="134" t="n">
+      <c r="D152" s="133" t="n">
         <v>1358.22</v>
       </c>
       <c r="E152" t="n">
         <v>15429</v>
       </c>
       <c r="F152" t="n">
-        <v>2986.290322580646</v>
+        <v>2986.290322580645</v>
       </c>
       <c r="G152" t="n">
         <v>1345.856666666667</v>
       </c>
       <c r="H152" t="n">
-        <v>-0.111951925547573</v>
+        <v>-0.1119519255475731</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -5933,27 +5921,27 @@
           <t>2032-08</t>
         </is>
       </c>
-      <c r="C153" s="90" t="n">
+      <c r="C153" s="89" t="n">
         <v>33336.28</v>
       </c>
-      <c r="D153" s="14" t="n">
+      <c r="D153" s="13" t="n">
         <v>1799.6</v>
       </c>
       <c r="E153" t="n">
         <v>15566</v>
       </c>
       <c r="F153" t="n">
-        <v>2845.290322580646</v>
+        <v>2845.290322580645</v>
       </c>
       <c r="G153" t="n">
         <v>1455.923333333334</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1150879810273399</v>
+        <v>0.11508798102734</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -5961,10 +5949,10 @@
           <t>2032-09</t>
         </is>
       </c>
-      <c r="C154" s="60" t="n">
+      <c r="C154" s="59" t="n">
         <v>31113.55</v>
       </c>
-      <c r="D154" s="66" t="n">
+      <c r="D154" s="65" t="n">
         <v>1772.04</v>
       </c>
       <c r="E154" t="n">
@@ -5977,11 +5965,11 @@
         <v>1643.286666666668</v>
       </c>
       <c r="H154" t="n">
-        <v>-0.0666760058410836</v>
+        <v>-0.06667600584108369</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -5989,10 +5977,10 @@
           <t>2032-10</t>
         </is>
       </c>
-      <c r="C155" s="152" t="n">
+      <c r="C155" s="151" t="n">
         <v>37989.34</v>
       </c>
-      <c r="D155" s="21" t="n">
+      <c r="D155" s="20" t="n">
         <v>1568.98</v>
       </c>
       <c r="E155" t="n">
@@ -6005,11 +5993,11 @@
         <v>1713.540000000001</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2209902116601931</v>
+        <v>0.2209902116601932</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -6017,10 +6005,10 @@
           <t>2032-11</t>
         </is>
       </c>
-      <c r="C156" s="59" t="n">
+      <c r="C156" s="58" t="n">
         <v>27378.3</v>
       </c>
-      <c r="D156" s="153" t="n">
+      <c r="D156" s="152" t="n">
         <v>1176.04</v>
       </c>
       <c r="E156" t="n">
@@ -6037,7 +6025,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -6045,10 +6033,10 @@
           <t>2032-12</t>
         </is>
       </c>
-      <c r="C157" s="75" t="n">
+      <c r="C157" s="74" t="n">
         <v>29244.8</v>
       </c>
-      <c r="D157" s="154" t="n">
+      <c r="D157" s="153" t="n">
         <v>1269.46</v>
       </c>
       <c r="E157" t="n">
@@ -6058,14 +6046,14 @@
         <v>2300.83870967742</v>
       </c>
       <c r="G157" t="n">
-        <v>1338.16</v>
+        <v>1338.160000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0681744301143607</v>
+        <v>0.06817443011436075</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -6073,10 +6061,10 @@
           <t>2033-01</t>
         </is>
       </c>
-      <c r="C158" s="155" t="n">
+      <c r="C158" s="154" t="n">
         <v>35747.61</v>
       </c>
-      <c r="D158" s="97" t="n">
+      <c r="D158" s="96" t="n">
         <v>1482.03</v>
       </c>
       <c r="E158" t="n">
@@ -6093,7 +6081,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -6101,10 +6089,10 @@
           <t>2033-02</t>
         </is>
       </c>
-      <c r="C159" s="59" t="n">
+      <c r="C159" s="58" t="n">
         <v>27359.03</v>
       </c>
-      <c r="D159" s="156" t="n">
+      <c r="D159" s="155" t="n">
         <v>1229.8</v>
       </c>
       <c r="E159" t="n">
@@ -6117,11 +6105,11 @@
         <v>1327.096666666667</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.2346612822507575</v>
+        <v>-0.2346612822507576</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -6129,10 +6117,10 @@
           <t>2033-03</t>
         </is>
       </c>
-      <c r="C160" s="27" t="n">
+      <c r="C160" s="26" t="n">
         <v>26559.93</v>
       </c>
-      <c r="D160" s="157" t="n">
+      <c r="D160" s="156" t="n">
         <v>1047.16</v>
       </c>
       <c r="E160" t="n">
@@ -6145,11 +6133,11 @@
         <v>1252.996666666667</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.0292079068592708</v>
+        <v>-0.02920790685927088</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -6157,10 +6145,10 @@
           <t>2033-04</t>
         </is>
       </c>
-      <c r="C161" s="144" t="n">
+      <c r="C161" s="143" t="n">
         <v>30121.79</v>
       </c>
-      <c r="D161" s="137" t="n">
+      <c r="D161" s="136" t="n">
         <v>1471.8</v>
       </c>
       <c r="E161" t="n">
@@ -6177,7 +6165,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -6185,10 +6173,10 @@
           <t>2033-05</t>
         </is>
       </c>
-      <c r="C162" s="33" t="n">
+      <c r="C162" s="32" t="n">
         <v>31811.05</v>
       </c>
-      <c r="D162" s="108" t="n">
+      <c r="D162" s="107" t="n">
         <v>1743.9</v>
       </c>
       <c r="E162" t="n">
@@ -6201,11 +6189,11 @@
         <v>1420.953333333334</v>
       </c>
       <c r="H162" t="n">
-        <v>0.0560809965144832</v>
+        <v>0.05608099651448328</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -6213,10 +6201,10 @@
           <t>2033-06</t>
         </is>
       </c>
-      <c r="C163" s="81" t="n">
+      <c r="C163" s="80" t="n">
         <v>31933.63</v>
       </c>
-      <c r="D163" s="158" t="n">
+      <c r="D163" s="157" t="n">
         <v>2337.53</v>
       </c>
       <c r="E163" t="n">
@@ -6229,11 +6217,11 @@
         <v>1851.076666666667</v>
       </c>
       <c r="H163" t="n">
-        <v>0.0038533779928673</v>
+        <v>0.003853377992867335</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -6241,17 +6229,17 @@
           <t>2033-07</t>
         </is>
       </c>
-      <c r="C164" s="159" t="n">
+      <c r="C164" s="158" t="n">
         <v>36613.9</v>
       </c>
-      <c r="D164" s="27" t="n">
+      <c r="D164" s="26" t="n">
         <v>1531.89</v>
       </c>
       <c r="E164" t="n">
         <v>15520</v>
       </c>
       <c r="F164" t="n">
-        <v>2432.290322580646</v>
+        <v>2432.290322580645</v>
       </c>
       <c r="G164" t="n">
         <v>1871.106666666667</v>
@@ -6261,7 +6249,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -6269,10 +6257,10 @@
           <t>2033-08</t>
         </is>
       </c>
-      <c r="C165" s="160" t="n">
+      <c r="C165" s="159" t="n">
         <v>34712.94</v>
       </c>
-      <c r="D165" s="139" t="n">
+      <c r="D165" s="138" t="n">
         <v>1545.16</v>
       </c>
       <c r="E165" t="n">
@@ -6285,11 +6273,11 @@
         <v>1804.860000000001</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.0519190799122737</v>
+        <v>-0.05191907991227374</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -6297,10 +6285,10 @@
           <t>2033-09</t>
         </is>
       </c>
-      <c r="C166" s="37" t="n">
+      <c r="C166" s="36" t="n">
         <v>27660.66</v>
       </c>
-      <c r="D166" s="104" t="n">
+      <c r="D166" s="103" t="n">
         <v>1554.95</v>
       </c>
       <c r="E166" t="n">
@@ -6313,11 +6301,11 @@
         <v>1544.000000000001</v>
       </c>
       <c r="H166" t="n">
-        <v>-0.2031599743496229</v>
+        <v>-0.203159974349623</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -6325,16 +6313,16 @@
           <t>2033-10</t>
         </is>
       </c>
-      <c r="C167" s="68" t="n">
+      <c r="C167" s="67" t="n">
         <v>32326.98</v>
       </c>
-      <c r="D167" s="146" t="n">
+      <c r="D167" s="145" t="n">
         <v>1157.77</v>
       </c>
       <c r="E167" t="n">
         <v>15411</v>
       </c>
-      <c r="F167" s="116" t="n">
+      <c r="F167" s="115" t="n">
         <v>3161.096774193548</v>
       </c>
       <c r="G167" t="n">
@@ -6345,7 +6333,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -6353,10 +6341,10 @@
           <t>2033-11</t>
         </is>
       </c>
-      <c r="C168" s="161" t="n">
+      <c r="C168" s="160" t="n">
         <v>35350.27</v>
       </c>
-      <c r="D168" s="162" t="n">
+      <c r="D168" s="161" t="n">
         <v>939.04</v>
       </c>
       <c r="E168" t="n">
@@ -6369,11 +6357,11 @@
         <v>1217.253333333334</v>
       </c>
       <c r="H168" t="n">
-        <v>0.09352219106145999</v>
+        <v>0.09352219106146009</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -6381,10 +6369,10 @@
           <t>2033-12</t>
         </is>
       </c>
-      <c r="C169" s="163" t="n">
+      <c r="C169" s="162" t="n">
         <v>35279.31</v>
       </c>
-      <c r="D169" s="9" t="n">
+      <c r="D169" s="8" t="n">
         <v>1189.42</v>
       </c>
       <c r="E169" t="n">
@@ -6394,14 +6382,14 @@
         <v>2775.741935483871</v>
       </c>
       <c r="G169" t="n">
-        <v>1095.41</v>
+        <v>1095.410000000001</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.0020073396893431</v>
+        <v>-0.002007339689343191</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" t="n">
         <v>168</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -6409,10 +6397,10 @@
           <t>2034-01</t>
         </is>
       </c>
-      <c r="C170" s="16" t="n">
+      <c r="C170" s="15" t="n">
         <v>31705.56</v>
       </c>
-      <c r="D170" s="164" t="n">
+      <c r="D170" s="163" t="n">
         <v>1508.92</v>
       </c>
       <c r="E170" t="n">
@@ -6425,11 +6413,11 @@
         <v>1212.460000000001</v>
       </c>
       <c r="H170" t="n">
-        <v>-0.1012987498905164</v>
+        <v>-0.1012987498905165</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" t="n">
         <v>169</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -6437,10 +6425,10 @@
           <t>2034-02</t>
         </is>
       </c>
-      <c r="C171" s="35" t="n">
+      <c r="C171" s="34" t="n">
         <v>30338.85</v>
       </c>
-      <c r="D171" s="61" t="n">
+      <c r="D171" s="60" t="n">
         <v>1282.44</v>
       </c>
       <c r="E171" t="n">
@@ -6453,11 +6441,11 @@
         <v>1326.926666666667</v>
       </c>
       <c r="H171" t="n">
-        <v>-0.0431063195225065</v>
+        <v>-0.04310631952250654</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" t="n">
         <v>170</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -6465,10 +6453,10 @@
           <t>2034-03</t>
         </is>
       </c>
-      <c r="C172" s="108" t="n">
+      <c r="C172" s="107" t="n">
         <v>28973.66</v>
       </c>
-      <c r="D172" s="61" t="n">
+      <c r="D172" s="60" t="n">
         <v>1285.4</v>
       </c>
       <c r="E172" t="n">
@@ -6481,11 +6469,11 @@
         <v>1358.920000000001</v>
       </c>
       <c r="H172" t="n">
-        <v>-0.0449980800195128</v>
+        <v>-0.04499808001951289</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" t="n">
         <v>171</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -6493,10 +6481,10 @@
           <t>2034-04</t>
         </is>
       </c>
-      <c r="C173" s="165" t="n">
+      <c r="C173" s="164" t="n">
         <v>20948.44</v>
       </c>
-      <c r="D173" s="80" t="n">
+      <c r="D173" s="79" t="n">
         <v>1561.79</v>
       </c>
       <c r="E173" t="n">
@@ -6513,7 +6501,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -6521,10 +6509,10 @@
           <t>2034-05</t>
         </is>
       </c>
-      <c r="C174" s="30" t="n">
+      <c r="C174" s="29" t="n">
         <v>28540.34</v>
       </c>
-      <c r="D174" s="166" t="n">
+      <c r="D174" s="165" t="n">
         <v>1162.24</v>
       </c>
       <c r="E174" t="n">
@@ -6541,7 +6529,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -6549,10 +6537,10 @@
           <t>2034-06</t>
         </is>
       </c>
-      <c r="C175" s="57" t="n">
+      <c r="C175" s="56" t="n">
         <v>30544.1</v>
       </c>
-      <c r="D175" s="167" t="n">
+      <c r="D175" s="166" t="n">
         <v>1616.97</v>
       </c>
       <c r="E175" t="n">
@@ -6569,7 +6557,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" t="n">
         <v>174</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -6577,10 +6565,10 @@
           <t>2034-07</t>
         </is>
       </c>
-      <c r="C176" s="53" t="n">
+      <c r="C176" s="52" t="n">
         <v>31217.11</v>
       </c>
-      <c r="D176" s="9" t="n">
+      <c r="D176" s="8" t="n">
         <v>1183.32</v>
       </c>
       <c r="E176" t="n">
@@ -6593,11 +6581,11 @@
         <v>1320.843333333334</v>
       </c>
       <c r="H176" t="n">
-        <v>0.022034042581055</v>
+        <v>0.02203404258105501</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" t="n">
         <v>175</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -6605,10 +6593,10 @@
           <t>2034-08</t>
         </is>
       </c>
-      <c r="C177" s="114" t="n">
+      <c r="C177" s="113" t="n">
         <v>33753.29</v>
       </c>
-      <c r="D177" s="32" t="n">
+      <c r="D177" s="31" t="n">
         <v>1272.41</v>
       </c>
       <c r="E177" t="n">
@@ -6621,11 +6609,11 @@
         <v>1357.566666666667</v>
       </c>
       <c r="H177" t="n">
-        <v>0.08124326691356119</v>
+        <v>0.08124326691356121</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" t="n">
         <v>176</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -6633,10 +6621,10 @@
           <t>2034-09</t>
         </is>
       </c>
-      <c r="C178" s="41" t="n">
+      <c r="C178" s="40" t="n">
         <v>34870.76</v>
       </c>
-      <c r="D178" s="102" t="n">
+      <c r="D178" s="101" t="n">
         <v>1823.19</v>
       </c>
       <c r="E178" t="n">
@@ -6649,11 +6637,11 @@
         <v>1426.306666666667</v>
       </c>
       <c r="H178" t="n">
-        <v>0.0331069949033115</v>
+        <v>0.03310699490331159</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" t="n">
         <v>177</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -6661,10 +6649,10 @@
           <t>2034-10</t>
         </is>
       </c>
-      <c r="C179" s="125" t="n">
+      <c r="C179" s="124" t="n">
         <v>26490.25</v>
       </c>
-      <c r="D179" s="66" t="n">
+      <c r="D179" s="65" t="n">
         <v>1768.12</v>
       </c>
       <c r="E179" t="n">
@@ -6681,7 +6669,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" t="n">
         <v>178</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -6689,10 +6677,10 @@
           <t>2034-11</t>
         </is>
       </c>
-      <c r="C180" s="115" t="n">
+      <c r="C180" s="114" t="n">
         <v>39065.76</v>
       </c>
-      <c r="D180" s="76" t="n">
+      <c r="D180" s="75" t="n">
         <v>2399.43</v>
       </c>
       <c r="E180" t="n">
@@ -6709,7 +6697,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -6717,10 +6705,10 @@
           <t>2034-12</t>
         </is>
       </c>
-      <c r="C181" s="128" t="n">
+      <c r="C181" s="127" t="n">
         <v>35237.07</v>
       </c>
-      <c r="D181" s="168" t="n">
+      <c r="D181" s="167" t="n">
         <v>1363.55</v>
       </c>
       <c r="E181" t="n">
@@ -6733,11 +6721,11 @@
         <v>1843.700000000001</v>
       </c>
       <c r="H181" t="n">
-        <v>-0.0980062847874968</v>
+        <v>-0.09800628478749684</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -6745,10 +6733,10 @@
           <t>2035-01</t>
         </is>
       </c>
-      <c r="C182" s="26" t="n">
+      <c r="C182" s="25" t="n">
         <v>31411</v>
       </c>
-      <c r="D182" s="12" t="n">
+      <c r="D182" s="11" t="n">
         <v>1809.6</v>
       </c>
       <c r="E182" t="n">
@@ -6761,11 +6749,11 @@
         <v>1857.526666666667</v>
       </c>
       <c r="H182" t="n">
-        <v>-0.1085808212771379</v>
+        <v>-0.108580821277138</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -6773,10 +6761,10 @@
           <t>2035-02</t>
         </is>
       </c>
-      <c r="C183" s="68" t="n">
+      <c r="C183" s="67" t="n">
         <v>32320.38</v>
       </c>
-      <c r="D183" s="169" t="n">
+      <c r="D183" s="168" t="n">
         <v>1174.35</v>
       </c>
       <c r="E183" t="n">
@@ -6789,11 +6777,11 @@
         <v>1449.166666666667</v>
       </c>
       <c r="H183" t="n">
-        <v>0.0289510044252014</v>
+        <v>0.02895100442520149</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" t="n">
         <v>182</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -6801,10 +6789,10 @@
           <t>2035-03</t>
         </is>
       </c>
-      <c r="C184" s="93" t="n">
+      <c r="C184" s="92" t="n">
         <v>28374.11</v>
       </c>
-      <c r="D184" s="170" t="n">
+      <c r="D184" s="169" t="n">
         <v>1462.61</v>
       </c>
       <c r="E184" t="n">
@@ -6817,11 +6805,11 @@
         <v>1482.186666666667</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.1220985025547348</v>
+        <v>-0.1220985025547349</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" t="n">
         <v>183</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -6829,10 +6817,10 @@
           <t>2035-04</t>
         </is>
       </c>
-      <c r="C185" s="62" t="n">
+      <c r="C185" s="61" t="n">
         <v>31983.92</v>
       </c>
-      <c r="D185" s="110" t="n">
+      <c r="D185" s="109" t="n">
         <v>1403.5</v>
       </c>
       <c r="E185" t="n">
@@ -6849,7 +6837,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -6857,10 +6845,10 @@
           <t>2035-05</t>
         </is>
       </c>
-      <c r="C186" s="80" t="n">
+      <c r="C186" s="79" t="n">
         <v>26922.93</v>
       </c>
-      <c r="D186" s="127" t="n">
+      <c r="D186" s="126" t="n">
         <v>1708.26</v>
       </c>
       <c r="E186" t="n">
@@ -6877,7 +6865,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -6885,10 +6873,10 @@
           <t>2035-06</t>
         </is>
       </c>
-      <c r="C187" s="5" t="n">
+      <c r="C187" s="4" t="n">
         <v>29349.64</v>
       </c>
-      <c r="D187" s="171" t="n">
+      <c r="D187" s="170" t="n">
         <v>1215.41</v>
       </c>
       <c r="E187" t="n">
@@ -6901,11 +6889,11 @@
         <v>1442.390000000001</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0901354347390865</v>
+        <v>0.09013543473908658</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" t="n">
         <v>186</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -6913,10 +6901,10 @@
           <t>2035-07</t>
         </is>
       </c>
-      <c r="C188" s="86" t="n">
+      <c r="C188" s="85" t="n">
         <v>28734.91</v>
       </c>
-      <c r="D188" s="8" t="n">
+      <c r="D188" s="7" t="n">
         <v>1321.69</v>
       </c>
       <c r="E188" t="n">
@@ -6929,11 +6917,11 @@
         <v>1415.120000000001</v>
       </c>
       <c r="H188" t="n">
-        <v>-0.0209450609956374</v>
+        <v>-0.02094506099563742</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" t="n">
         <v>187</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -6941,10 +6929,10 @@
           <t>2035-08</t>
         </is>
       </c>
-      <c r="C189" s="172" t="n">
+      <c r="C189" s="171" t="n">
         <v>22066.64</v>
       </c>
-      <c r="D189" s="44" t="n">
+      <c r="D189" s="43" t="n">
         <v>1224.67</v>
       </c>
       <c r="E189" t="n">
@@ -6957,11 +6945,11 @@
         <v>1253.923333333334</v>
       </c>
       <c r="H189" t="n">
-        <v>-0.2320616281728392</v>
+        <v>-0.2320616281728393</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" t="n">
         <v>188</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -6969,10 +6957,10 @@
           <t>2035-09</t>
         </is>
       </c>
-      <c r="C190" s="161" t="n">
+      <c r="C190" s="160" t="n">
         <v>35393.83</v>
       </c>
-      <c r="D190" s="100" t="n">
+      <c r="D190" s="99" t="n">
         <v>1938.45</v>
       </c>
       <c r="E190" t="n">
@@ -6984,12 +6972,12 @@
       <c r="G190" t="n">
         <v>1494.936666666667</v>
       </c>
-      <c r="H190" s="116" t="n">
+      <c r="H190" s="115" t="n">
         <v>0.6039519383104996</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" t="n">
         <v>189</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -6997,10 +6985,10 @@
           <t>2035-10</t>
         </is>
       </c>
-      <c r="C191" s="131" t="n">
+      <c r="C191" s="130" t="n">
         <v>27418.88</v>
       </c>
-      <c r="D191" s="46" t="n">
+      <c r="D191" s="45" t="n">
         <v>1411.56</v>
       </c>
       <c r="E191" t="n">
@@ -7017,7 +7005,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" t="n">
         <v>190</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -7025,10 +7013,10 @@
           <t>2035-11</t>
         </is>
       </c>
-      <c r="C192" s="108" t="n">
+      <c r="C192" s="107" t="n">
         <v>28988.18</v>
       </c>
-      <c r="D192" s="146" t="n">
+      <c r="D192" s="145" t="n">
         <v>1155.71</v>
       </c>
       <c r="E192" t="n">
@@ -7041,11 +7029,11 @@
         <v>1501.906666666667</v>
       </c>
       <c r="H192" t="n">
-        <v>0.0572342852807992</v>
+        <v>0.05723428528079921</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" t="n">
         <v>191</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -7053,10 +7041,10 @@
           <t>2035-12</t>
         </is>
       </c>
-      <c r="C193" s="20" t="n">
+      <c r="C193" s="19" t="n">
         <v>29840.37</v>
       </c>
-      <c r="D193" s="111" t="n">
+      <c r="D193" s="110" t="n">
         <v>1190.67</v>
       </c>
       <c r="E193" t="n">
@@ -7069,11 +7057,11 @@
         <v>1252.646666666667</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0293978442247839</v>
+        <v>0.02939784422478398</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" t="n">
         <v>192</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -7081,10 +7069,10 @@
           <t>2036-01</t>
         </is>
       </c>
-      <c r="C194" s="141" t="n">
+      <c r="C194" s="140" t="n">
         <v>33076.51</v>
       </c>
-      <c r="D194" s="173" t="n">
+      <c r="D194" s="172" t="n">
         <v>1853.08</v>
       </c>
       <c r="E194" t="n">
@@ -7101,7 +7089,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" t="n">
         <v>193</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -7109,10 +7097,10 @@
           <t>2036-02</t>
         </is>
       </c>
-      <c r="C195" s="112" t="n">
+      <c r="C195" s="111" t="n">
         <v>27237.48</v>
       </c>
-      <c r="D195" s="46" t="n">
+      <c r="D195" s="45" t="n">
         <v>1412.53</v>
       </c>
       <c r="E195" t="n">
@@ -7129,7 +7117,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" t="n">
         <v>194</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -7137,10 +7125,10 @@
           <t>2036-03</t>
         </is>
       </c>
-      <c r="C196" s="174" t="n">
+      <c r="C196" s="173" t="n">
         <v>36170.38</v>
       </c>
-      <c r="D196" s="46" t="n">
+      <c r="D196" s="45" t="n">
         <v>1410.97</v>
       </c>
       <c r="E196" t="n">
@@ -7157,7 +7145,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -7165,10 +7153,10 @@
           <t>2036-04</t>
         </is>
       </c>
-      <c r="C197" s="159" t="n">
+      <c r="C197" s="158" t="n">
         <v>36563.4</v>
       </c>
-      <c r="D197" s="137" t="n">
+      <c r="D197" s="136" t="n">
         <v>1474.72</v>
       </c>
       <c r="E197" t="n">
@@ -7181,11 +7169,11 @@
         <v>1432.740000000001</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0108657968204923</v>
+        <v>0.01086579682049238</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" t="n">
         <v>196</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -7193,10 +7181,10 @@
           <t>2036-05</t>
         </is>
       </c>
-      <c r="C198" s="175" t="n">
+      <c r="C198" s="174" t="n">
         <v>24572.86</v>
       </c>
-      <c r="D198" s="48" t="n">
+      <c r="D198" s="47" t="n">
         <v>1370.62</v>
       </c>
       <c r="E198" t="n">
@@ -7213,7 +7201,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -7221,10 +7209,10 @@
           <t>2036-06</t>
         </is>
       </c>
-      <c r="C199" s="39" t="n">
+      <c r="C199" s="38" t="n">
         <v>32570.34</v>
       </c>
-      <c r="D199" s="66" t="n">
+      <c r="D199" s="65" t="n">
         <v>1772.04</v>
       </c>
       <c r="E199" t="n">
@@ -7241,7 +7229,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" t="n">
         <v>198</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -7249,10 +7237,10 @@
           <t>2036-07</t>
         </is>
       </c>
-      <c r="C200" s="86" t="n">
+      <c r="C200" s="85" t="n">
         <v>28731.3</v>
       </c>
-      <c r="D200" s="57" t="n">
+      <c r="D200" s="56" t="n">
         <v>1881.09</v>
       </c>
       <c r="E200" t="n">
@@ -7269,7 +7257,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" t="n">
         <v>199</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -7277,10 +7265,10 @@
           <t>2036-08</t>
         </is>
       </c>
-      <c r="C201" s="35" t="n">
+      <c r="C201" s="34" t="n">
         <v>30322.79</v>
       </c>
-      <c r="D201" s="71" t="n">
+      <c r="D201" s="70" t="n">
         <v>1134.26</v>
       </c>
       <c r="E201" t="n">
@@ -7293,11 +7281,11 @@
         <v>1595.796666666667</v>
       </c>
       <c r="H201" t="n">
-        <v>0.0553922029285136</v>
+        <v>0.05539220292851366</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" t="n">
         <v>200</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -7305,10 +7293,10 @@
           <t>2036-09</t>
         </is>
       </c>
-      <c r="C202" s="19" t="n">
+      <c r="C202" s="18" t="n">
         <v>27913.63</v>
       </c>
-      <c r="D202" s="71" t="n">
+      <c r="D202" s="70" t="n">
         <v>1131.26</v>
       </c>
       <c r="E202" t="n">
@@ -7321,11 +7309,11 @@
         <v>1382.203333333334</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.0794504727302468</v>
+        <v>-0.07945047273024686</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" t="n">
         <v>201</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -7333,10 +7321,10 @@
           <t>2036-10</t>
         </is>
       </c>
-      <c r="C203" s="59" t="n">
+      <c r="C203" s="58" t="n">
         <v>27350.21</v>
       </c>
-      <c r="D203" s="86" t="n">
+      <c r="D203" s="85" t="n">
         <v>1721.04</v>
       </c>
       <c r="E203" t="n">
@@ -7349,11 +7337,11 @@
         <v>1328.853333333334</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.0201844045364217</v>
+        <v>-0.02018440453642179</v>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" t="n">
         <v>202</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -7361,10 +7349,10 @@
           <t>2036-11</t>
         </is>
       </c>
-      <c r="C204" s="62" t="n">
+      <c r="C204" s="61" t="n">
         <v>32033.55</v>
       </c>
-      <c r="D204" s="65" t="n">
+      <c r="D204" s="64" t="n">
         <v>1892.55</v>
       </c>
       <c r="E204" t="n">
@@ -7374,14 +7362,14 @@
         <v>2574.5</v>
       </c>
       <c r="G204" t="n">
-        <v>1581.616666666668</v>
+        <v>1581.616666666667</v>
       </c>
       <c r="H204" t="n">
         <v>0.1712359795409248</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" t="n">
         <v>203</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -7389,10 +7377,10 @@
           <t>2036-12</t>
         </is>
       </c>
-      <c r="C205" s="82" t="n">
+      <c r="C205" s="81" t="n">
         <v>25350.54</v>
       </c>
-      <c r="D205" s="32" t="n">
+      <c r="D205" s="31" t="n">
         <v>1272.66</v>
       </c>
       <c r="E205" t="n">
@@ -7409,7 +7397,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" t="n">
         <v>204</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -7417,10 +7405,10 @@
           <t>2037-01</t>
         </is>
       </c>
-      <c r="C206" s="42" t="n">
+      <c r="C206" s="41" t="n">
         <v>30042.56</v>
       </c>
-      <c r="D206" s="123" t="n">
+      <c r="D206" s="122" t="n">
         <v>1081.54</v>
       </c>
       <c r="E206" t="n">
@@ -7437,7 +7425,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" t="n">
         <v>205</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -7445,10 +7433,10 @@
           <t>2037-02</t>
         </is>
       </c>
-      <c r="C207" s="79" t="n">
+      <c r="C207" s="78" t="n">
         <v>24094.2</v>
       </c>
-      <c r="D207" s="145" t="n">
+      <c r="D207" s="144" t="n">
         <v>1251.21</v>
       </c>
       <c r="E207" t="n">
@@ -7461,11 +7449,11 @@
         <v>1201.803333333334</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.1979977738248671</v>
+        <v>-0.1979977738248672</v>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" t="n">
         <v>206</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -7473,13 +7461,13 @@
           <t>2037-03</t>
         </is>
       </c>
-      <c r="C208" s="121" t="n">
+      <c r="C208" s="120" t="n">
         <v>28820</v>
       </c>
-      <c r="D208" s="55" t="n">
+      <c r="D208" s="54" t="n">
         <v>1641.75</v>
       </c>
-      <c r="E208" s="116" t="n">
+      <c r="E208" s="115" t="n">
         <v>15835</v>
       </c>
       <c r="F208" t="n">
@@ -7493,7 +7481,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" t="n">
         <v>207</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -7501,10 +7489,10 @@
           <t>2037-04</t>
         </is>
       </c>
-      <c r="C209" s="119" t="n">
+      <c r="C209" s="118" t="n">
         <v>28136.82</v>
       </c>
-      <c r="D209" s="132" t="n">
+      <c r="D209" s="131" t="n">
         <v>874.97</v>
       </c>
       <c r="E209" t="n">
@@ -7517,11 +7505,11 @@
         <v>1255.976666666667</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.0237050659264399</v>
+        <v>-0.02370506592643995</v>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" t="n">
         <v>208</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -7529,10 +7517,10 @@
           <t>2037-05</t>
         </is>
       </c>
-      <c r="C210" s="59" t="n">
+      <c r="C210" s="58" t="n">
         <v>27365.59</v>
       </c>
-      <c r="D210" s="123" t="n">
+      <c r="D210" s="122" t="n">
         <v>1081.86</v>
       </c>
       <c r="E210" t="n">
@@ -7545,11 +7533,11 @@
         <v>1199.526666666667</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.0274099916053057</v>
+        <v>-0.02740999160530577</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" t="n">
         <v>209</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -7557,10 +7545,10 @@
           <t>2037-06</t>
         </is>
       </c>
-      <c r="C211" s="65" t="n">
+      <c r="C211" s="64" t="n">
         <v>30655.96</v>
       </c>
-      <c r="D211" s="79" t="n">
+      <c r="D211" s="78" t="n">
         <v>1306.24</v>
       </c>
       <c r="E211" t="n">
@@ -7573,11 +7561,11 @@
         <v>1087.690000000001</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1202374953362963</v>
+        <v>0.1202374953362964</v>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" t="n">
         <v>210</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -7585,27 +7573,27 @@
           <t>2037-07</t>
         </is>
       </c>
-      <c r="C212" s="58" t="n">
+      <c r="C212" s="57" t="n">
         <v>30836.97</v>
       </c>
-      <c r="D212" s="176" t="n">
+      <c r="D212" s="175" t="n">
         <v>1016.41</v>
       </c>
       <c r="E212" t="n">
         <v>15439</v>
       </c>
       <c r="F212" t="n">
-        <v>2518.709677419354</v>
+        <v>2518.709677419355</v>
       </c>
       <c r="G212" t="n">
         <v>1134.836666666667</v>
       </c>
       <c r="H212" t="n">
-        <v>0.0059045614621104</v>
+        <v>0.005904561462110491</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" t="n">
         <v>211</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -7613,10 +7601,10 @@
           <t>2037-08</t>
         </is>
       </c>
-      <c r="C213" s="119" t="n">
+      <c r="C213" s="118" t="n">
         <v>28121.09</v>
       </c>
-      <c r="D213" s="177" t="n">
+      <c r="D213" s="176" t="n">
         <v>716.6799999999999</v>
       </c>
       <c r="E213" t="n">
@@ -7629,11 +7617,11 @@
         <v>1013.110000000001</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.0880722068348479</v>
+        <v>-0.08807220683484795</v>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" t="n">
         <v>212</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -7641,10 +7629,10 @@
           <t>2037-09</t>
         </is>
       </c>
-      <c r="C214" s="80" t="n">
+      <c r="C214" s="79" t="n">
         <v>26955.86</v>
       </c>
-      <c r="D214" s="178" t="n">
+      <c r="D214" s="177" t="n">
         <v>972.99</v>
       </c>
       <c r="E214" t="n">
@@ -7657,11 +7645,11 @@
         <v>902.0266666666672</v>
       </c>
       <c r="H214" t="n">
-        <v>-0.0414361605471196</v>
+        <v>-0.04143616054711963</v>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" t="n">
         <v>213</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -7669,10 +7657,10 @@
           <t>2037-10</t>
         </is>
       </c>
-      <c r="C215" s="102" t="n">
+      <c r="C215" s="101" t="n">
         <v>29917.16</v>
       </c>
-      <c r="D215" s="140" t="n">
+      <c r="D215" s="139" t="n">
         <v>1072.45</v>
       </c>
       <c r="E215" t="n">
@@ -7682,14 +7670,14 @@
         <v>2323.41935483871</v>
       </c>
       <c r="G215" t="n">
-        <v>920.7066666666672</v>
+        <v>920.7066666666673</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1098573742407031</v>
+        <v>0.1098573742407032</v>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" t="n">
         <v>214</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -7697,10 +7685,10 @@
           <t>2037-11</t>
         </is>
       </c>
-      <c r="C216" s="10" t="n">
+      <c r="C216" s="9" t="n">
         <v>30920.18</v>
       </c>
-      <c r="D216" s="111" t="n">
+      <c r="D216" s="110" t="n">
         <v>1195.49</v>
       </c>
       <c r="E216" t="n">
@@ -7713,11 +7701,11 @@
         <v>1080.310000000001</v>
       </c>
       <c r="H216" t="n">
-        <v>0.0335265780575428</v>
+        <v>0.03352657805754289</v>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" t="n">
         <v>215</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -7725,27 +7713,27 @@
           <t>2037-12</t>
         </is>
       </c>
-      <c r="C217" s="24" t="n">
+      <c r="C217" s="23" t="n">
         <v>33935.1</v>
       </c>
-      <c r="D217" s="179" t="n">
+      <c r="D217" s="178" t="n">
         <v>2347.57</v>
       </c>
       <c r="E217" t="n">
         <v>15583</v>
       </c>
       <c r="F217" t="n">
-        <v>2384.709677419354</v>
+        <v>2384.709677419355</v>
       </c>
       <c r="G217" t="n">
         <v>1538.503333333334</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0975065475039278</v>
+        <v>0.09750654750392784</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" t="n">
         <v>216</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -7753,10 +7741,10 @@
           <t>2038-01</t>
         </is>
       </c>
-      <c r="C218" s="180" t="n">
+      <c r="C218" s="179" t="n">
         <v>36495.94</v>
       </c>
-      <c r="D218" s="31" t="n">
+      <c r="D218" s="30" t="n">
         <v>1873.6</v>
       </c>
       <c r="E218" t="n">
@@ -7769,11 +7757,11 @@
         <v>1805.553333333334</v>
       </c>
       <c r="H218" t="n">
-        <v>0.07546286882902969</v>
+        <v>0.07546286882902975</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" t="n">
         <v>217</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -7781,10 +7769,10 @@
           <t>2038-02</t>
         </is>
       </c>
-      <c r="C219" s="33" t="n">
+      <c r="C219" s="32" t="n">
         <v>31800.63</v>
       </c>
-      <c r="D219" s="92" t="n">
+      <c r="D219" s="91" t="n">
         <v>2055.77</v>
       </c>
       <c r="E219" t="n">
@@ -7801,7 +7789,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" t="n">
         <v>218</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -7809,10 +7797,10 @@
           <t>2038-03</t>
         </is>
       </c>
-      <c r="C220" s="181" t="n">
+      <c r="C220" s="180" t="n">
         <v>27095.81</v>
       </c>
-      <c r="D220" s="35" t="n">
+      <c r="D220" s="34" t="n">
         <v>1863.2</v>
       </c>
       <c r="E220" t="n">
@@ -7829,7 +7817,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" t="n">
         <v>219</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -7837,10 +7825,10 @@
           <t>2038-04</t>
         </is>
       </c>
-      <c r="C221" s="91" t="n">
+      <c r="C221" s="90" t="n">
         <v>31611.93</v>
       </c>
-      <c r="D221" s="87" t="n">
+      <c r="D221" s="86" t="n">
         <v>2027.07</v>
       </c>
       <c r="E221" t="n">
@@ -7857,7 +7845,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" t="n">
         <v>220</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -7865,10 +7853,10 @@
           <t>2038-05</t>
         </is>
       </c>
-      <c r="C222" s="55" t="n">
+      <c r="C222" s="54" t="n">
         <v>27879.17</v>
       </c>
-      <c r="D222" s="182" t="n">
+      <c r="D222" s="181" t="n">
         <v>1684.89</v>
       </c>
       <c r="E222" t="n">
@@ -7885,7 +7873,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" t="n">
         <v>221</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -7893,10 +7881,10 @@
           <t>2038-06</t>
         </is>
       </c>
-      <c r="C223" s="144" t="n">
+      <c r="C223" s="143" t="n">
         <v>30181.89</v>
       </c>
-      <c r="D223" s="93" t="n">
+      <c r="D223" s="92" t="n">
         <v>1690.88</v>
       </c>
       <c r="E223" t="n">
@@ -7909,11 +7897,11 @@
         <v>1800.946666666667</v>
       </c>
       <c r="H223" t="n">
-        <v>0.0825964331075852</v>
+        <v>0.08259643310758524</v>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" t="n">
         <v>222</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -7921,10 +7909,10 @@
           <t>2038-07</t>
         </is>
       </c>
-      <c r="C224" s="183" t="n">
+      <c r="C224" s="182" t="n">
         <v>38937.44</v>
       </c>
-      <c r="D224" s="100" t="n">
+      <c r="D224" s="99" t="n">
         <v>1935.29</v>
       </c>
       <c r="E224" t="n">
@@ -7937,11 +7925,11 @@
         <v>1770.353333333334</v>
       </c>
       <c r="H224" t="n">
-        <v>0.2900928338152448</v>
+        <v>0.2900928338152449</v>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" t="n">
         <v>223</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -7949,10 +7937,10 @@
           <t>2038-08</t>
         </is>
       </c>
-      <c r="C225" s="175" t="n">
+      <c r="C225" s="174" t="n">
         <v>24557.47</v>
       </c>
-      <c r="D225" s="184" t="n">
+      <c r="D225" s="183" t="n">
         <v>1008.69</v>
       </c>
       <c r="E225" t="n">
@@ -7969,7 +7957,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" t="n">
         <v>224</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -7977,10 +7965,10 @@
           <t>2038-09</t>
         </is>
       </c>
-      <c r="C226" s="127" t="n">
+      <c r="C226" s="126" t="n">
         <v>28645.75</v>
       </c>
-      <c r="D226" s="4" t="n">
+      <c r="D226" s="3" t="n">
         <v>1488.17</v>
       </c>
       <c r="E226" t="n">
@@ -7997,7 +7985,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" t="n">
         <v>225</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -8005,10 +7993,10 @@
           <t>2038-10</t>
         </is>
       </c>
-      <c r="C227" s="57" t="n">
+      <c r="C227" s="56" t="n">
         <v>30594.58</v>
       </c>
-      <c r="D227" s="97" t="n">
+      <c r="D227" s="96" t="n">
         <v>1478.04</v>
       </c>
       <c r="E227" t="n">
@@ -8021,11 +8009,11 @@
         <v>1324.966666666667</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0680320815478736</v>
+        <v>0.06803208154787366</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" t="n">
         <v>226</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -8033,10 +8021,10 @@
           <t>2038-11</t>
         </is>
       </c>
-      <c r="C228" s="101" t="n">
+      <c r="C228" s="100" t="n">
         <v>32049.5</v>
       </c>
-      <c r="D228" s="70" t="n">
+      <c r="D228" s="69" t="n">
         <v>1345.91</v>
       </c>
       <c r="E228" t="n">
@@ -8049,11 +8037,11 @@
         <v>1437.373333333334</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0475548283388755</v>
+        <v>0.04755482833887559</v>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" t="n">
         <v>227</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -8061,10 +8049,10 @@
           <t>2038-12</t>
         </is>
       </c>
-      <c r="C229" s="18" t="n">
+      <c r="C229" s="17" t="n">
         <v>29510.58</v>
       </c>
-      <c r="D229" s="185" t="n">
+      <c r="D229" s="184" t="n">
         <v>1389.05</v>
       </c>
       <c r="E229" t="n">
@@ -8077,11 +8065,11 @@
         <v>1404.333333333334</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.07921870856019581</v>
+        <v>-0.07921870856019586</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" t="n">
         <v>228</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -8089,10 +8077,10 @@
           <t>2039-01</t>
         </is>
       </c>
-      <c r="C230" s="114" t="n">
+      <c r="C230" s="113" t="n">
         <v>33758.46</v>
       </c>
-      <c r="D230" s="170" t="n">
+      <c r="D230" s="169" t="n">
         <v>1460.12</v>
       </c>
       <c r="E230" t="n">
@@ -8105,11 +8093,11 @@
         <v>1398.360000000001</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1439443074314363</v>
+        <v>0.1439443074314364</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" t="n">
         <v>229</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -8117,10 +8105,10 @@
           <t>2039-02</t>
         </is>
       </c>
-      <c r="C231" s="112" t="n">
+      <c r="C231" s="111" t="n">
         <v>27287.15</v>
       </c>
-      <c r="D231" s="51" t="n">
+      <c r="D231" s="50" t="n">
         <v>1288.78</v>
       </c>
       <c r="E231" t="n">
@@ -8137,7 +8125,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" t="n">
         <v>230</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -8145,10 +8133,10 @@
           <t>2039-03</t>
         </is>
       </c>
-      <c r="C232" s="186" t="n">
+      <c r="C232" s="185" t="n">
         <v>27206.63</v>
       </c>
-      <c r="D232" s="187" t="n">
+      <c r="D232" s="186" t="n">
         <v>1264.2</v>
       </c>
       <c r="E232" t="n">
@@ -8161,11 +8149,11 @@
         <v>1337.700000000001</v>
       </c>
       <c r="H232" t="n">
-        <v>-0.0029508394977123</v>
+        <v>-0.002950839497712354</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" t="n">
         <v>231</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -8173,10 +8161,10 @@
           <t>2039-04</t>
         </is>
       </c>
-      <c r="C233" s="167" t="n">
+      <c r="C233" s="166" t="n">
         <v>27522.98</v>
       </c>
-      <c r="D233" s="145" t="n">
+      <c r="D233" s="144" t="n">
         <v>1253.23</v>
       </c>
       <c r="E233" t="n">
@@ -8189,11 +8177,11 @@
         <v>1268.736666666667</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0116276804587704</v>
+        <v>0.0116276804587705</v>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" t="n">
         <v>232</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -8201,10 +8189,10 @@
           <t>2039-05</t>
         </is>
       </c>
-      <c r="C234" s="143" t="n">
+      <c r="C234" s="142" t="n">
         <v>33030.32</v>
       </c>
-      <c r="D234" s="51" t="n">
+      <c r="D234" s="50" t="n">
         <v>1291.92</v>
       </c>
       <c r="E234" t="n">
@@ -8217,11 +8205,11 @@
         <v>1269.783333333334</v>
       </c>
       <c r="H234" t="n">
-        <v>0.2000996985064844</v>
+        <v>0.2000996985064845</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" t="n">
         <v>233</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -8229,10 +8217,10 @@
           <t>2039-06</t>
         </is>
       </c>
-      <c r="C235" s="41" t="n">
+      <c r="C235" s="40" t="n">
         <v>34892.83</v>
       </c>
-      <c r="D235" s="174" t="n">
+      <c r="D235" s="173" t="n">
         <v>2381.64</v>
       </c>
       <c r="E235" t="n">
@@ -8249,7 +8237,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" t="n">
         <v>234</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -8257,10 +8245,10 @@
           <t>2039-07</t>
         </is>
       </c>
-      <c r="C236" s="121" t="n">
+      <c r="C236" s="120" t="n">
         <v>28815.07</v>
       </c>
-      <c r="D236" s="188" t="n">
+      <c r="D236" s="187" t="n">
         <v>1055.5</v>
       </c>
       <c r="E236" t="n">
@@ -8277,7 +8265,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" t="n">
         <v>235</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -8285,10 +8273,10 @@
           <t>2039-08</t>
         </is>
       </c>
-      <c r="C237" s="73" t="n">
+      <c r="C237" s="72" t="n">
         <v>32416.14</v>
       </c>
-      <c r="D237" s="189" t="n">
+      <c r="D237" s="188" t="n">
         <v>2232.4</v>
       </c>
       <c r="E237" t="n">
@@ -8305,7 +8293,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" t="n">
         <v>236</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -8313,10 +8301,10 @@
           <t>2039-09</t>
         </is>
       </c>
-      <c r="C238" s="186" t="n">
+      <c r="C238" s="185" t="n">
         <v>27205.09</v>
       </c>
-      <c r="D238" s="42" t="n">
+      <c r="D238" s="41" t="n">
         <v>1842.3</v>
       </c>
       <c r="E238" t="n">
@@ -8333,7 +8321,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" t="n">
         <v>237</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -8341,10 +8329,10 @@
           <t>2039-10</t>
         </is>
       </c>
-      <c r="C239" s="190" t="n">
+      <c r="C239" s="189" t="n">
         <v>34273.05</v>
       </c>
-      <c r="D239" s="17" t="n">
+      <c r="D239" s="16" t="n">
         <v>1498.71</v>
       </c>
       <c r="E239" t="n">
@@ -8361,7 +8349,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" t="n">
         <v>238</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -8369,10 +8357,10 @@
           <t>2039-11</t>
         </is>
       </c>
-      <c r="C240" s="190" t="n">
+      <c r="C240" s="189" t="n">
         <v>34303.77</v>
       </c>
-      <c r="D240" s="191" t="n">
+      <c r="D240" s="190" t="n">
         <v>1437.35</v>
       </c>
       <c r="E240" t="n">
@@ -8385,11 +8373,11 @@
         <v>1592.786666666667</v>
       </c>
       <c r="H240" t="n">
-        <v>0.0008963310822935</v>
+        <v>0.0008963310822935888</v>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" t="n">
         <v>239</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -8397,10 +8385,10 @@
           <t>2039-12</t>
         </is>
       </c>
-      <c r="C241" s="91" t="n">
+      <c r="C241" s="90" t="n">
         <v>31550.56</v>
       </c>
-      <c r="D241" s="192" t="n">
+      <c r="D241" s="191" t="n">
         <v>1236.24</v>
       </c>
       <c r="E241" t="n">
@@ -8413,11 +8401,11 @@
         <v>1390.766666666667</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.0802596915732586</v>
+        <v>-0.08025969157325863</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" t="n">
         <v>240</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -8425,10 +8413,10 @@
           <t>2040-01</t>
         </is>
       </c>
-      <c r="C242" s="79" t="n">
+      <c r="C242" s="78" t="n">
         <v>24034.13</v>
       </c>
-      <c r="D242" s="98" t="n">
+      <c r="D242" s="97" t="n">
         <v>1118.75</v>
       </c>
       <c r="E242" t="n">
@@ -8445,7 +8433,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" t="n">
         <v>241</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -8453,10 +8441,10 @@
           <t>2040-02</t>
         </is>
       </c>
-      <c r="C243" s="107" t="n">
+      <c r="C243" s="106" t="n">
         <v>34646.49</v>
       </c>
-      <c r="D243" s="88" t="n">
+      <c r="D243" s="87" t="n">
         <v>2077.49</v>
       </c>
       <c r="E243" t="n">
@@ -8473,7 +8461,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" t="n">
         <v>242</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -8481,10 +8469,10 @@
           <t>2040-03</t>
         </is>
       </c>
-      <c r="C244" s="190" t="n">
+      <c r="C244" s="189" t="n">
         <v>34278.42</v>
       </c>
-      <c r="D244" s="58" t="n">
+      <c r="D244" s="57" t="n">
         <v>1907.83</v>
       </c>
       <c r="E244" t="n">
@@ -8497,11 +8485,11 @@
         <v>1701.356666666667</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.0106235869780748</v>
+        <v>-0.01062358697807486</v>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" t="n">
         <v>243</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -8509,10 +8497,10 @@
           <t>2040-04</t>
         </is>
       </c>
-      <c r="C245" s="34" t="n">
+      <c r="C245" s="33" t="n">
         <v>27600.19</v>
       </c>
-      <c r="D245" s="50" t="n">
+      <c r="D245" s="49" t="n">
         <v>1655.68</v>
       </c>
       <c r="E245" t="n">
@@ -8529,7 +8517,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" t="n">
         <v>244</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -8537,10 +8525,10 @@
           <t>2040-05</t>
         </is>
       </c>
-      <c r="C246" s="74" t="n">
+      <c r="C246" s="73" t="n">
         <v>33730.98</v>
       </c>
-      <c r="D246" s="193" t="n">
+      <c r="D246" s="192" t="n">
         <v>2222.41</v>
       </c>
       <c r="E246" t="n">
@@ -8557,7 +8545,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" t="n">
         <v>245</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -8565,10 +8553,10 @@
           <t>2040-06</t>
         </is>
       </c>
-      <c r="C247" s="73" t="n">
+      <c r="C247" s="72" t="n">
         <v>32448.48</v>
       </c>
-      <c r="D247" s="21" t="n">
+      <c r="D247" s="20" t="n">
         <v>1570.7</v>
       </c>
       <c r="E247" t="n">
@@ -8581,11 +8569,11 @@
         <v>1816.263333333334</v>
       </c>
       <c r="H247" t="n">
-        <v>-0.0380214271865212</v>
+        <v>-0.03802142718652124</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" t="n">
         <v>246</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -8593,10 +8581,10 @@
           <t>2040-07</t>
         </is>
       </c>
-      <c r="C248" s="102" t="n">
+      <c r="C248" s="101" t="n">
         <v>29852.1</v>
       </c>
-      <c r="D248" s="28" t="n">
+      <c r="D248" s="27" t="n">
         <v>1733.53</v>
       </c>
       <c r="E248" t="n">
@@ -8609,11 +8597,11 @@
         <v>1842.213333333334</v>
       </c>
       <c r="H248" t="n">
-        <v>-0.0800154583512078</v>
+        <v>-0.08001545835120782</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" t="n">
         <v>247</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -8621,10 +8609,10 @@
           <t>2040-08</t>
         </is>
       </c>
-      <c r="C249" s="5" t="n">
+      <c r="C249" s="4" t="n">
         <v>29392.13</v>
       </c>
-      <c r="D249" s="3" t="n">
+      <c r="D249" s="2" t="n">
         <v>1491.29</v>
       </c>
       <c r="E249" t="n">
@@ -8637,11 +8625,11 @@
         <v>1598.506666666667</v>
       </c>
       <c r="H249" t="n">
-        <v>-0.0154082962337657</v>
+        <v>-0.01540829623376572</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" t="n">
         <v>248</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -8649,10 +8637,10 @@
           <t>2040-09</t>
         </is>
       </c>
-      <c r="C250" s="139" t="n">
+      <c r="C250" s="138" t="n">
         <v>26793.26</v>
       </c>
-      <c r="D250" s="28" t="n">
+      <c r="D250" s="27" t="n">
         <v>1735.76</v>
       </c>
       <c r="E250" t="n">
@@ -8665,11 +8653,11 @@
         <v>1653.526666666667</v>
       </c>
       <c r="H250" t="n">
-        <v>-0.08842060782937471</v>
+        <v>-0.08842060782937478</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" t="n">
         <v>249</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -8677,10 +8665,10 @@
           <t>2040-10</t>
         </is>
       </c>
-      <c r="C251" s="49" t="n">
+      <c r="C251" s="48" t="n">
         <v>34082.61</v>
       </c>
-      <c r="D251" s="35" t="n">
+      <c r="D251" s="34" t="n">
         <v>1861.53</v>
       </c>
       <c r="E251" t="n">
@@ -8697,7 +8685,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" t="n">
         <v>250</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -8705,10 +8693,10 @@
           <t>2040-11</t>
         </is>
       </c>
-      <c r="C252" s="144" t="n">
+      <c r="C252" s="143" t="n">
         <v>30164.85</v>
       </c>
-      <c r="D252" s="192" t="n">
+      <c r="D252" s="191" t="n">
         <v>1237.48</v>
       </c>
       <c r="E252" t="n">
@@ -8721,11 +8709,11 @@
         <v>1611.590000000001</v>
       </c>
       <c r="H252" t="n">
-        <v>-0.1149489431707254</v>
+        <v>-0.1149489431707255</v>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" t="n">
         <v>251</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -8733,10 +8721,10 @@
           <t>2040-12</t>
         </is>
       </c>
-      <c r="C253" s="19" t="n">
+      <c r="C253" s="18" t="n">
         <v>27972.77</v>
       </c>
-      <c r="D253" s="51" t="n">
+      <c r="D253" s="50" t="n">
         <v>1288.86</v>
       </c>
       <c r="E253" t="n">
@@ -8749,11 +8737,11 @@
         <v>1462.623333333334</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.07267001161948421</v>
+        <v>-0.07267001161948428</v>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" t="n">
         <v>252</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -8761,10 +8749,10 @@
           <t>2041-01</t>
         </is>
       </c>
-      <c r="C254" s="87" t="n">
+      <c r="C254" s="86" t="n">
         <v>32186.41</v>
       </c>
-      <c r="D254" s="110" t="n">
+      <c r="D254" s="109" t="n">
         <v>1404.15</v>
       </c>
       <c r="E254" t="n">
@@ -8781,7 +8769,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" t="n">
         <v>253</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -8789,10 +8777,10 @@
           <t>2041-02</t>
         </is>
       </c>
-      <c r="C255" s="194" t="n">
+      <c r="C255" s="193" t="n">
         <v>29020.04</v>
       </c>
-      <c r="D255" s="175" t="n">
+      <c r="D255" s="174" t="n">
         <v>1350.92</v>
       </c>
       <c r="E255" t="n">
@@ -8805,11 +8793,11 @@
         <v>1347.976666666667</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.0983759916063953</v>
+        <v>-0.09837599160639532</v>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" t="n">
         <v>254</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -8817,10 +8805,10 @@
           <t>2041-03</t>
         </is>
       </c>
-      <c r="C256" s="104" t="n">
+      <c r="C256" s="103" t="n">
         <v>26856.28</v>
       </c>
-      <c r="D256" s="79" t="n">
+      <c r="D256" s="78" t="n">
         <v>1307.67</v>
       </c>
       <c r="E256" t="n">
@@ -8833,11 +8821,11 @@
         <v>1354.246666666667</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.0745608896472921</v>
+        <v>-0.07456088964729213</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" t="n">
         <v>255</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -8845,10 +8833,10 @@
           <t>2041-04</t>
         </is>
       </c>
-      <c r="C257" s="81" t="n">
+      <c r="C257" s="80" t="n">
         <v>31920.11</v>
       </c>
-      <c r="D257" s="187" t="n">
+      <c r="D257" s="186" t="n">
         <v>1259.68</v>
       </c>
       <c r="E257" t="n">
@@ -8861,11 +8849,11 @@
         <v>1306.090000000001</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1885529194661361</v>
+        <v>0.1885529194661362</v>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" t="n">
         <v>256</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -8873,10 +8861,10 @@
           <t>2041-05</t>
         </is>
       </c>
-      <c r="C258" s="137" t="n">
+      <c r="C258" s="136" t="n">
         <v>25899.75</v>
       </c>
-      <c r="D258" s="27" t="n">
+      <c r="D258" s="26" t="n">
         <v>1534.71</v>
       </c>
       <c r="E258" t="n">
@@ -8889,11 +8877,11 @@
         <v>1367.353333333334</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.188607119461681</v>
+        <v>-0.1886071194616811</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" t="n">
         <v>257</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -8901,10 +8889,10 @@
           <t>2041-06</t>
         </is>
       </c>
-      <c r="C259" s="144" t="n">
+      <c r="C259" s="143" t="n">
         <v>30110.47</v>
       </c>
-      <c r="D259" s="37" t="n">
+      <c r="D259" s="36" t="n">
         <v>1625.26</v>
       </c>
       <c r="E259" t="n">
@@ -8921,7 +8909,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" t="n">
         <v>258</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -8929,10 +8917,10 @@
           <t>2041-07</t>
         </is>
       </c>
-      <c r="C260" s="47" t="n">
+      <c r="C260" s="46" t="n">
         <v>31521.02</v>
       </c>
-      <c r="D260" s="120" t="n">
+      <c r="D260" s="119" t="n">
         <v>1518.39</v>
       </c>
       <c r="E260" t="n">
@@ -8945,11 +8933,11 @@
         <v>1559.453333333334</v>
       </c>
       <c r="H260" t="n">
-        <v>0.046845831366963</v>
+        <v>0.04684583136696308</v>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" t="n">
         <v>259</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -8957,10 +8945,10 @@
           <t>2041-08</t>
         </is>
       </c>
-      <c r="C261" s="73" t="n">
+      <c r="C261" s="72" t="n">
         <v>32454.91</v>
       </c>
-      <c r="D261" s="40" t="n">
+      <c r="D261" s="39" t="n">
         <v>1829.98</v>
       </c>
       <c r="E261" t="n">
@@ -8973,11 +8961,11 @@
         <v>1657.876666666667</v>
       </c>
       <c r="H261" t="n">
-        <v>0.0296275310887781</v>
+        <v>0.02962753108877814</v>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" t="n">
         <v>260</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -8985,10 +8973,10 @@
           <t>2041-09</t>
         </is>
       </c>
-      <c r="C262" s="101" t="n">
+      <c r="C262" s="100" t="n">
         <v>32074.27</v>
       </c>
-      <c r="D262" s="186" t="n">
+      <c r="D262" s="185" t="n">
         <v>1585.84</v>
       </c>
       <c r="E262" t="n">
@@ -9001,11 +8989,11 @@
         <v>1644.736666666667</v>
       </c>
       <c r="H262" t="n">
-        <v>-0.0117282716236156</v>
+        <v>-0.01172827162361567</v>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" t="n">
         <v>261</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -9013,27 +9001,27 @@
           <t>2041-10</t>
         </is>
       </c>
-      <c r="C263" s="95" t="n">
+      <c r="C263" s="94" t="n">
         <v>30699.35</v>
       </c>
-      <c r="D263" s="195" t="n">
+      <c r="D263" s="194" t="n">
         <v>1326.27</v>
       </c>
       <c r="E263" t="n">
         <v>15619</v>
       </c>
       <c r="F263" t="n">
-        <v>2561.709677419354</v>
+        <v>2561.709677419355</v>
       </c>
       <c r="G263" t="n">
         <v>1580.696666666667</v>
       </c>
       <c r="H263" t="n">
-        <v>-0.042866758931692</v>
+        <v>-0.04286675893169201</v>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" t="n">
         <v>262</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -9041,10 +9029,10 @@
           <t>2041-11</t>
         </is>
       </c>
-      <c r="C264" s="14" t="n">
+      <c r="C264" s="13" t="n">
         <v>29676.81</v>
       </c>
-      <c r="D264" s="181" t="n">
+      <c r="D264" s="180" t="n">
         <v>1574.66</v>
       </c>
       <c r="E264" t="n">
@@ -9057,11 +9045,11 @@
         <v>1495.59</v>
       </c>
       <c r="H264" t="n">
-        <v>-0.0333081970790911</v>
+        <v>-0.03330819707909116</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" t="n">
         <v>263</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -9069,10 +9057,10 @@
           <t>2041-12</t>
         </is>
       </c>
-      <c r="C265" s="196" t="n">
+      <c r="C265" s="195" t="n">
         <v>33409.27</v>
       </c>
-      <c r="D265" s="63" t="n">
+      <c r="D265" s="62" t="n">
         <v>1439.15</v>
       </c>
       <c r="E265" t="n">
@@ -9085,11 +9073,11 @@
         <v>1446.693333333334</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1257702563045015</v>
+        <v>0.1257702563045016</v>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" t="n">
         <v>264</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -9097,10 +9085,10 @@
           <t>2042-01</t>
         </is>
       </c>
-      <c r="C266" s="197" t="n">
+      <c r="C266" s="196" t="n">
         <v>21883.39</v>
       </c>
-      <c r="D266" s="64" t="n">
+      <c r="D266" s="63" t="n">
         <v>921.3099999999999</v>
       </c>
       <c r="E266" t="n">
@@ -9117,7 +9105,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" t="n">
         <v>265</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -9125,10 +9113,10 @@
           <t>2042-02</t>
         </is>
       </c>
-      <c r="C267" s="15" t="n">
+      <c r="C267" s="14" t="n">
         <v>27777.23</v>
       </c>
-      <c r="D267" s="170" t="n">
+      <c r="D267" s="169" t="n">
         <v>1465.52</v>
       </c>
       <c r="E267" t="n">
@@ -9145,7 +9133,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" t="n">
         <v>266</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -9153,10 +9141,10 @@
           <t>2042-03</t>
         </is>
       </c>
-      <c r="C268" s="129" t="n">
+      <c r="C268" s="128" t="n">
         <v>33898.18</v>
       </c>
-      <c r="D268" s="70" t="n">
+      <c r="D268" s="69" t="n">
         <v>1346.3</v>
       </c>
       <c r="E268" t="n">
@@ -9173,7 +9161,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" t="n">
         <v>267</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -9181,10 +9169,10 @@
           <t>2042-04</t>
         </is>
       </c>
-      <c r="C269" s="111" t="n">
+      <c r="C269" s="110" t="n">
         <v>22827.55</v>
       </c>
-      <c r="D269" s="157" t="n">
+      <c r="D269" s="156" t="n">
         <v>1048.58</v>
       </c>
       <c r="E269" t="n">
@@ -9201,7 +9189,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" t="n">
         <v>268</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -9209,10 +9197,10 @@
           <t>2042-05</t>
         </is>
       </c>
-      <c r="C270" s="40" t="n">
+      <c r="C270" s="39" t="n">
         <v>29940.99</v>
       </c>
-      <c r="D270" s="130" t="n">
+      <c r="D270" s="129" t="n">
         <v>1090.32</v>
       </c>
       <c r="E270" t="n">
@@ -9229,7 +9217,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" t="n">
         <v>269</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -9237,10 +9225,10 @@
           <t>2042-06</t>
         </is>
       </c>
-      <c r="C271" s="16" t="n">
+      <c r="C271" s="15" t="n">
         <v>31666.78</v>
       </c>
-      <c r="D271" s="191" t="n">
+      <c r="D271" s="190" t="n">
         <v>1434.38</v>
       </c>
       <c r="E271" t="n">
@@ -9253,11 +9241,11 @@
         <v>1191.093333333334</v>
       </c>
       <c r="H271" t="n">
-        <v>0.0576397106441703</v>
+        <v>0.05763971064417039</v>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" t="n">
         <v>270</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -9265,10 +9253,10 @@
           <t>2042-07</t>
         </is>
       </c>
-      <c r="C272" s="81" t="n">
+      <c r="C272" s="80" t="n">
         <v>31959.41</v>
       </c>
-      <c r="D272" s="109" t="n">
+      <c r="D272" s="108" t="n">
         <v>1336.05</v>
       </c>
       <c r="E272" t="n">
@@ -9281,11 +9269,11 @@
         <v>1286.916666666667</v>
       </c>
       <c r="H272" t="n">
-        <v>0.009240914295674999</v>
+        <v>0.009240914295675084</v>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" t="n">
         <v>271</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -9293,10 +9281,10 @@
           <t>2042-08</t>
         </is>
       </c>
-      <c r="C273" s="22" t="n">
+      <c r="C273" s="21" t="n">
         <v>34519.36</v>
       </c>
-      <c r="D273" s="198" t="n">
+      <c r="D273" s="197" t="n">
         <v>2375.27</v>
       </c>
       <c r="E273" t="n">
@@ -9309,11 +9297,11 @@
         <v>1715.233333333334</v>
       </c>
       <c r="H273" t="n">
-        <v>0.0801000393937185</v>
+        <v>0.08010003939371857</v>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" t="n">
         <v>272</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -9321,10 +9309,10 @@
           <t>2042-09</t>
         </is>
       </c>
-      <c r="C274" s="33" t="n">
+      <c r="C274" s="32" t="n">
         <v>31839.9</v>
       </c>
-      <c r="D274" s="142" t="n">
+      <c r="D274" s="141" t="n">
         <v>1146.2</v>
       </c>
       <c r="E274" t="n">
@@ -9341,7 +9329,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" t="n">
         <v>273</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -9349,10 +9337,10 @@
           <t>2042-10</t>
         </is>
       </c>
-      <c r="C275" s="199" t="n">
+      <c r="C275" s="198" t="n">
         <v>34063.9</v>
       </c>
-      <c r="D275" s="101" t="n">
+      <c r="D275" s="100" t="n">
         <v>2020.24</v>
       </c>
       <c r="E275" t="n">
@@ -9365,11 +9353,11 @@
         <v>1847.236666666667</v>
       </c>
       <c r="H275" t="n">
-        <v>0.069849465607618</v>
+        <v>0.06984946560761807</v>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" t="n">
         <v>274</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -9377,10 +9365,10 @@
           <t>2042-11</t>
         </is>
       </c>
-      <c r="C276" s="84" t="n">
+      <c r="C276" s="83" t="n">
         <v>32918.16</v>
       </c>
-      <c r="D276" s="139" t="n">
+      <c r="D276" s="138" t="n">
         <v>1548.67</v>
       </c>
       <c r="E276" t="n">
@@ -9393,11 +9381,11 @@
         <v>1571.703333333334</v>
       </c>
       <c r="H276" t="n">
-        <v>-0.0336350212394941</v>
+        <v>-0.03363502123949413</v>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" t="n">
         <v>275</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -9405,10 +9393,10 @@
           <t>2042-12</t>
         </is>
       </c>
-      <c r="C277" s="128" t="n">
+      <c r="C277" s="127" t="n">
         <v>35221.26</v>
       </c>
-      <c r="D277" s="46" t="n">
+      <c r="D277" s="45" t="n">
         <v>1412.32</v>
       </c>
       <c r="E277" t="n">
@@ -9421,11 +9409,11 @@
         <v>1660.410000000001</v>
       </c>
       <c r="H277" t="n">
-        <v>0.0699644208546288</v>
+        <v>0.06996442085462884</v>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" t="n">
         <v>276</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -9433,10 +9421,10 @@
           <t>2043-01</t>
         </is>
       </c>
-      <c r="C278" s="14" t="n">
+      <c r="C278" s="13" t="n">
         <v>29613.43</v>
       </c>
-      <c r="D278" s="97" t="n">
+      <c r="D278" s="96" t="n">
         <v>1478.25</v>
       </c>
       <c r="E278" t="n">
@@ -9453,7 +9441,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" t="n">
         <v>277</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -9461,10 +9449,10 @@
           <t>2043-02</t>
         </is>
       </c>
-      <c r="C279" s="99" t="n">
+      <c r="C279" s="98" t="n">
         <v>33555.58</v>
       </c>
-      <c r="D279" s="70" t="n">
+      <c r="D279" s="69" t="n">
         <v>1342.05</v>
       </c>
       <c r="E279" t="n">
@@ -9477,11 +9465,11 @@
         <v>1410.873333333334</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1331203443842878</v>
+        <v>0.1331203443842879</v>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" t="n">
         <v>278</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -9489,17 +9477,17 @@
           <t>2043-03</t>
         </is>
       </c>
-      <c r="C280" s="144" t="n">
+      <c r="C280" s="143" t="n">
         <v>30186.18</v>
       </c>
-      <c r="D280" s="11" t="n">
+      <c r="D280" s="10" t="n">
         <v>1756.07</v>
       </c>
       <c r="E280" t="n">
         <v>15387</v>
       </c>
       <c r="F280" t="n">
-        <v>2505.290322580646</v>
+        <v>2505.290322580645</v>
       </c>
       <c r="G280" t="n">
         <v>1525.456666666667</v>
@@ -9509,7 +9497,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" t="n">
         <v>279</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -9517,10 +9505,10 @@
           <t>2043-04</t>
         </is>
       </c>
-      <c r="C281" s="88" t="n">
+      <c r="C281" s="87" t="n">
         <v>32762.01</v>
       </c>
-      <c r="D281" s="59" t="n">
+      <c r="D281" s="58" t="n">
         <v>1602.32</v>
       </c>
       <c r="E281" t="n">
@@ -9533,11 +9521,11 @@
         <v>1566.813333333334</v>
       </c>
       <c r="H281" t="n">
-        <v>0.0853314331260199</v>
+        <v>0.08533143312601998</v>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" t="n">
         <v>280</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -9545,10 +9533,10 @@
           <t>2043-05</t>
         </is>
       </c>
-      <c r="C282" s="200" t="n">
+      <c r="C282" s="199" t="n">
         <v>37283.61</v>
       </c>
-      <c r="D282" s="99" t="n">
+      <c r="D282" s="98" t="n">
         <v>2146.65</v>
       </c>
       <c r="E282" t="n">
@@ -9561,11 +9549,11 @@
         <v>1835.013333333334</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1380135101600907</v>
+        <v>0.1380135101600908</v>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" t="n">
         <v>281</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -9573,10 +9561,10 @@
           <t>2043-06</t>
         </is>
       </c>
-      <c r="C283" s="101" t="n">
+      <c r="C283" s="100" t="n">
         <v>32126.87</v>
       </c>
-      <c r="D283" s="14" t="n">
+      <c r="D283" s="13" t="n">
         <v>1803.79</v>
       </c>
       <c r="E283" t="n">
@@ -9589,11 +9577,11 @@
         <v>1850.920000000001</v>
       </c>
       <c r="H283" t="n">
-        <v>-0.1383111774852274</v>
+        <v>-0.1383111774852275</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" t="n">
         <v>282</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -9601,10 +9589,10 @@
           <t>2043-07</t>
         </is>
       </c>
-      <c r="C284" s="3" t="n">
+      <c r="C284" s="2" t="n">
         <v>26213.92</v>
       </c>
-      <c r="D284" s="17" t="n">
+      <c r="D284" s="16" t="n">
         <v>1498.29</v>
       </c>
       <c r="E284" t="n">
@@ -9617,11 +9605,11 @@
         <v>1816.243333333334</v>
       </c>
       <c r="H284" t="n">
-        <v>-0.1840499868178879</v>
+        <v>-0.184049986817888</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" t="n">
         <v>283</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -9629,17 +9617,17 @@
           <t>2043-08</t>
         </is>
       </c>
-      <c r="C285" s="147" t="n">
+      <c r="C285" s="146" t="n">
         <v>32678.16</v>
       </c>
-      <c r="D285" s="201" t="n">
+      <c r="D285" s="200" t="n">
         <v>1198.16</v>
       </c>
       <c r="E285" t="n">
         <v>15458</v>
       </c>
       <c r="F285" t="n">
-        <v>2745.290322580646</v>
+        <v>2745.290322580645</v>
       </c>
       <c r="G285" t="n">
         <v>1500.080000000001</v>
@@ -9649,7 +9637,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" t="n">
         <v>284</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -9657,17 +9645,17 @@
           <t>2043-09</t>
         </is>
       </c>
-      <c r="C286" s="17" t="n">
+      <c r="C286" s="16" t="n">
         <v>26250.8</v>
       </c>
-      <c r="D286" s="192" t="n">
+      <c r="D286" s="191" t="n">
         <v>1236.89</v>
       </c>
       <c r="E286" t="n">
         <v>14774</v>
       </c>
       <c r="F286" t="n">
-        <v>1894.933333333334</v>
+        <v>1894.933333333333</v>
       </c>
       <c r="G286" t="n">
         <v>1311.113333333334</v>
@@ -9677,7 +9665,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" t="n">
         <v>285</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -9685,10 +9673,10 @@
           <t>2043-10</t>
         </is>
       </c>
-      <c r="C287" s="26" t="n">
+      <c r="C287" s="25" t="n">
         <v>31423.22</v>
       </c>
-      <c r="D287" s="53" t="n">
+      <c r="D287" s="52" t="n">
         <v>1941.43</v>
       </c>
       <c r="E287" t="n">
@@ -9705,7 +9693,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" t="n">
         <v>286</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -9713,10 +9701,10 @@
           <t>2043-11</t>
         </is>
       </c>
-      <c r="C288" s="99" t="n">
+      <c r="C288" s="98" t="n">
         <v>33564.46</v>
       </c>
-      <c r="D288" s="181" t="n">
+      <c r="D288" s="180" t="n">
         <v>1572.78</v>
       </c>
       <c r="E288" t="n">
@@ -9729,11 +9717,11 @@
         <v>1583.700000000001</v>
       </c>
       <c r="H288" t="n">
-        <v>0.0681419663548166</v>
+        <v>0.06814196635481662</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" t="n">
         <v>287</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -9741,10 +9729,10 @@
           <t>2043-12</t>
         </is>
       </c>
-      <c r="C289" s="174" t="n">
+      <c r="C289" s="173" t="n">
         <v>36141.98</v>
       </c>
-      <c r="D289" s="159" t="n">
+      <c r="D289" s="158" t="n">
         <v>2419.86</v>
       </c>
       <c r="E289" t="n">
@@ -9761,7 +9749,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" t="n">
         <v>288</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -9769,10 +9757,10 @@
           <t>2044-01</t>
         </is>
       </c>
-      <c r="C290" s="202" t="n">
+      <c r="C290" s="201" t="n">
         <v>37538.06</v>
       </c>
-      <c r="D290" s="51" t="n">
+      <c r="D290" s="50" t="n">
         <v>1292.36</v>
       </c>
       <c r="E290" t="n">
@@ -9785,11 +9773,11 @@
         <v>1761.666666666667</v>
       </c>
       <c r="H290" t="n">
-        <v>0.0386276568134893</v>
+        <v>0.03862765681348934</v>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" t="n">
         <v>289</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -9797,10 +9785,10 @@
           <t>2044-02</t>
         </is>
       </c>
-      <c r="C291" s="121" t="n">
+      <c r="C291" s="120" t="n">
         <v>28783.32</v>
       </c>
-      <c r="D291" s="38" t="n">
+      <c r="D291" s="37" t="n">
         <v>890.1</v>
       </c>
       <c r="E291" t="n">
@@ -9817,7 +9805,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" t="n">
         <v>290</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -9825,10 +9813,10 @@
           <t>2044-03</t>
         </is>
       </c>
-      <c r="C292" s="203" t="n">
+      <c r="C292" s="202" t="n">
         <v>37200.86</v>
       </c>
-      <c r="D292" s="93" t="n">
+      <c r="D292" s="92" t="n">
         <v>1691.26</v>
       </c>
       <c r="E292" t="n">
@@ -9841,11 +9829,11 @@
         <v>1291.24</v>
       </c>
       <c r="H292" t="n">
-        <v>0.2924450688801709</v>
+        <v>0.292445068880171</v>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" t="n">
         <v>291</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -9853,10 +9841,10 @@
           <t>2044-04</t>
         </is>
       </c>
-      <c r="C293" s="196" t="n">
+      <c r="C293" s="195" t="n">
         <v>33412.78</v>
       </c>
-      <c r="D293" s="204" t="n">
+      <c r="D293" s="203" t="n">
         <v>1699.25</v>
       </c>
       <c r="E293" t="n">
@@ -9873,7 +9861,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" t="n">
         <v>292</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -9881,10 +9869,10 @@
           <t>2044-05</t>
         </is>
       </c>
-      <c r="C294" s="101" t="n">
+      <c r="C294" s="100" t="n">
         <v>32082.06</v>
       </c>
-      <c r="D294" s="111" t="n">
+      <c r="D294" s="110" t="n">
         <v>1194.3</v>
       </c>
       <c r="E294" t="n">
@@ -9897,11 +9885,11 @@
         <v>1528.27</v>
       </c>
       <c r="H294" t="n">
-        <v>-0.0398266770978049</v>
+        <v>-0.03982667709780496</v>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" t="n">
         <v>293</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -9909,10 +9897,10 @@
           <t>2044-06</t>
         </is>
       </c>
-      <c r="C295" s="19" t="n">
+      <c r="C295" s="18" t="n">
         <v>27926.29</v>
       </c>
-      <c r="D295" s="112" t="n">
+      <c r="D295" s="111" t="n">
         <v>1595</v>
       </c>
       <c r="E295" t="n">
@@ -9925,11 +9913,11 @@
         <v>1496.183333333334</v>
       </c>
       <c r="H295" t="n">
-        <v>-0.1295356345571325</v>
+        <v>-0.1295356345571326</v>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" t="n">
         <v>294</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -9937,10 +9925,10 @@
           <t>2044-07</t>
         </is>
       </c>
-      <c r="C296" s="92" t="n">
+      <c r="C296" s="91" t="n">
         <v>32538.28</v>
       </c>
-      <c r="D296" s="43" t="n">
+      <c r="D296" s="42" t="n">
         <v>2262.99</v>
       </c>
       <c r="E296" t="n">
@@ -9957,7 +9945,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" t="n">
         <v>295</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -9965,10 +9953,10 @@
           <t>2044-08</t>
         </is>
       </c>
-      <c r="C297" s="83" t="n">
+      <c r="C297" s="82" t="n">
         <v>30418.19</v>
       </c>
-      <c r="D297" s="29" t="n">
+      <c r="D297" s="28" t="n">
         <v>1394.83</v>
       </c>
       <c r="E297" t="n">
@@ -9981,11 +9969,11 @@
         <v>1750.940000000001</v>
       </c>
       <c r="H297" t="n">
-        <v>-0.0651567937825845</v>
+        <v>-0.06515679378258454</v>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" t="n">
         <v>296</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -9993,10 +9981,10 @@
           <t>2044-09</t>
         </is>
       </c>
-      <c r="C298" s="4" t="n">
+      <c r="C298" s="3" t="n">
         <v>26076.42</v>
       </c>
-      <c r="D298" s="25" t="n">
+      <c r="D298" s="24" t="n">
         <v>1424.52</v>
       </c>
       <c r="E298" t="n">
@@ -10013,7 +10001,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" t="n">
         <v>297</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -10021,10 +10009,10 @@
           <t>2044-10</t>
         </is>
       </c>
-      <c r="C299" s="26" t="n">
+      <c r="C299" s="25" t="n">
         <v>31409.18</v>
       </c>
-      <c r="D299" s="20" t="n">
+      <c r="D299" s="19" t="n">
         <v>1815.89</v>
       </c>
       <c r="E299" t="n">
@@ -10041,7 +10029,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" t="n">
         <v>298</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -10049,10 +10037,10 @@
           <t>2044-11</t>
         </is>
       </c>
-      <c r="C300" s="120" t="n">
+      <c r="C300" s="119" t="n">
         <v>26398.47</v>
       </c>
-      <c r="D300" s="112" t="n">
+      <c r="D300" s="111" t="n">
         <v>1591.07</v>
       </c>
       <c r="E300" t="n">
@@ -10069,7 +10057,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" t="n">
         <v>299</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -10077,10 +10065,10 @@
           <t>2044-12</t>
         </is>
       </c>
-      <c r="C301" s="45" t="n">
+      <c r="C301" s="44" t="n">
         <v>25720.76</v>
       </c>
-      <c r="D301" s="187" t="n">
+      <c r="D301" s="186" t="n">
         <v>1257.81</v>
       </c>
       <c r="E301" t="n">
@@ -10093,11 +10081,11 @@
         <v>1554.923333333334</v>
       </c>
       <c r="H301" t="n">
-        <v>-0.0256723211610371</v>
+        <v>-0.02567232116103713</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" t="n">
         <v>300</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -10105,10 +10093,10 @@
           <t>2045-01</t>
         </is>
       </c>
-      <c r="C302" s="55" t="n">
+      <c r="C302" s="54" t="n">
         <v>27868.75</v>
       </c>
-      <c r="D302" s="140" t="n">
+      <c r="D302" s="139" t="n">
         <v>1072.48</v>
       </c>
       <c r="E302" t="n">
@@ -10121,11 +10109,11 @@
         <v>1307.120000000001</v>
       </c>
       <c r="H302" t="n">
-        <v>0.0835119179993126</v>
+        <v>0.08351191799931268</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" t="n">
         <v>301</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -10133,10 +10121,10 @@
           <t>2045-02</t>
         </is>
       </c>
-      <c r="C303" s="131" t="n">
+      <c r="C303" s="130" t="n">
         <v>27475.6</v>
       </c>
-      <c r="D303" s="171" t="n">
+      <c r="D303" s="170" t="n">
         <v>1213</v>
       </c>
       <c r="E303" t="n">
@@ -10149,11 +10137,11 @@
         <v>1181.096666666667</v>
       </c>
       <c r="H303" t="n">
-        <v>-0.0141071989235255</v>
+        <v>-0.01410719892352552</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" t="n">
         <v>302</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -10161,10 +10149,10 @@
           <t>2045-03</t>
         </is>
       </c>
-      <c r="C304" s="92" t="n">
+      <c r="C304" s="91" t="n">
         <v>32529.33</v>
       </c>
-      <c r="D304" s="175" t="n">
+      <c r="D304" s="174" t="n">
         <v>1351.3</v>
       </c>
       <c r="E304" t="n">
@@ -10181,7 +10169,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" t="n">
         <v>303</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -10189,10 +10177,10 @@
           <t>2045-04</t>
         </is>
       </c>
-      <c r="C305" s="35" t="n">
+      <c r="C305" s="34" t="n">
         <v>30323.99</v>
       </c>
-      <c r="D305" s="132" t="n">
+      <c r="D305" s="131" t="n">
         <v>878.79</v>
       </c>
       <c r="E305" t="n">
@@ -10205,11 +10193,11 @@
         <v>1147.696666666667</v>
       </c>
       <c r="H305" t="n">
-        <v>-0.0677954326141977</v>
+        <v>-0.06779543261419774</v>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" t="n">
         <v>304</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -10217,10 +10205,10 @@
           <t>2045-05</t>
         </is>
       </c>
-      <c r="C306" s="205" t="n">
+      <c r="C306" s="204" t="n">
         <v>34181.27</v>
       </c>
-      <c r="D306" s="109" t="n">
+      <c r="D306" s="108" t="n">
         <v>1334.42</v>
       </c>
       <c r="E306" t="n">
@@ -10233,11 +10221,11 @@
         <v>1188.170000000001</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1272022580141991</v>
+        <v>0.1272022580141992</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" t="n">
         <v>305</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -10245,10 +10233,10 @@
           <t>2045-06</t>
         </is>
       </c>
-      <c r="C307" s="133" t="n">
+      <c r="C307" s="132" t="n">
         <v>25679.86</v>
       </c>
-      <c r="D307" s="71" t="n">
+      <c r="D307" s="70" t="n">
         <v>1136.86</v>
       </c>
       <c r="E307" t="n">
@@ -10265,7 +10253,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" t="n">
         <v>306</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -10273,10 +10261,10 @@
           <t>2045-07</t>
         </is>
       </c>
-      <c r="C308" s="21" t="n">
+      <c r="C308" s="20" t="n">
         <v>26997.48</v>
       </c>
-      <c r="D308" s="206" t="n">
+      <c r="D308" s="205" t="n">
         <v>1382.79</v>
       </c>
       <c r="E308" t="n">
@@ -10289,11 +10277,11 @@
         <v>1284.690000000001</v>
       </c>
       <c r="H308" t="n">
-        <v>0.0513094697556761</v>
+        <v>0.05130946975567618</v>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" t="n">
         <v>307</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -10301,27 +10289,27 @@
           <t>2045-08</t>
         </is>
       </c>
-      <c r="C309" s="207" t="n">
+      <c r="C309" s="206" t="n">
         <v>35047.81</v>
       </c>
-      <c r="D309" s="21" t="n">
+      <c r="D309" s="20" t="n">
         <v>1565.38</v>
       </c>
       <c r="E309" t="n">
         <v>15466</v>
       </c>
       <c r="F309" t="n">
-        <v>2407.709677419354</v>
+        <v>2407.709677419355</v>
       </c>
       <c r="G309" t="n">
         <v>1361.676666666667</v>
       </c>
       <c r="H309" t="n">
-        <v>0.2981882012691554</v>
+        <v>0.2981882012691555</v>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" t="n">
         <v>308</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -10329,10 +10317,10 @@
           <t>2045-09</t>
         </is>
       </c>
-      <c r="C310" s="131" t="n">
+      <c r="C310" s="130" t="n">
         <v>27482.46</v>
       </c>
-      <c r="D310" s="25" t="n">
+      <c r="D310" s="24" t="n">
         <v>1429.63</v>
       </c>
       <c r="E310" t="n">
@@ -10345,11 +10333,11 @@
         <v>1459.266666666667</v>
       </c>
       <c r="H310" t="n">
-        <v>-0.2158579951215211</v>
+        <v>-0.2158579951215212</v>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" t="n">
         <v>309</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -10357,17 +10345,17 @@
           <t>2045-10</t>
         </is>
       </c>
-      <c r="C311" s="118" t="n">
+      <c r="C311" s="117" t="n">
         <v>31764.32</v>
       </c>
-      <c r="D311" s="83" t="n">
+      <c r="D311" s="82" t="n">
         <v>1870.82</v>
       </c>
       <c r="E311" t="n">
         <v>15483</v>
       </c>
       <c r="F311" t="n">
-        <v>2264.290322580646</v>
+        <v>2264.290322580645</v>
       </c>
       <c r="G311" t="n">
         <v>1621.943333333334</v>
@@ -10377,7 +10365,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" t="n">
         <v>310</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -10385,10 +10373,10 @@
           <t>2045-11</t>
         </is>
       </c>
-      <c r="C312" s="103" t="n">
+      <c r="C312" s="102" t="n">
         <v>33149.36</v>
       </c>
-      <c r="D312" s="12" t="n">
+      <c r="D312" s="11" t="n">
         <v>1807.99</v>
       </c>
       <c r="E312" t="n">
@@ -10401,11 +10389,11 @@
         <v>1702.813333333334</v>
       </c>
       <c r="H312" t="n">
-        <v>0.0436036408145994</v>
+        <v>0.04360364081459944</v>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" t="n">
         <v>311</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -10413,10 +10401,10 @@
           <t>2045-12</t>
         </is>
       </c>
-      <c r="C313" s="147" t="n">
+      <c r="C313" s="146" t="n">
         <v>32667.82</v>
       </c>
-      <c r="D313" s="51" t="n">
+      <c r="D313" s="50" t="n">
         <v>1292.89</v>
       </c>
       <c r="E313" t="n">
@@ -10429,11 +10417,11 @@
         <v>1657.233333333334</v>
       </c>
       <c r="H313" t="n">
-        <v>-0.0145263739631775</v>
+        <v>-0.01452637396317757</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" t="n">
         <v>312</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -10441,27 +10429,27 @@
           <t>2046-01</t>
         </is>
       </c>
-      <c r="C314" s="40" t="n">
+      <c r="C314" s="39" t="n">
         <v>29967.25</v>
       </c>
-      <c r="D314" s="18" t="n">
+      <c r="D314" s="17" t="n">
         <v>1783.51</v>
       </c>
       <c r="E314" t="n">
         <v>15584</v>
       </c>
       <c r="F314" t="n">
-        <v>2151.290322580646</v>
+        <v>2151.290322580645</v>
       </c>
       <c r="G314" t="n">
         <v>1628.130000000001</v>
       </c>
       <c r="H314" t="n">
-        <v>-0.0826675915319724</v>
+        <v>-0.08266759153197245</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" t="n">
         <v>313</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -10469,10 +10457,10 @@
           <t>2046-02</t>
         </is>
       </c>
-      <c r="C315" s="88" t="n">
+      <c r="C315" s="87" t="n">
         <v>32766.85</v>
       </c>
-      <c r="D315" s="104" t="n">
+      <c r="D315" s="103" t="n">
         <v>1551.37</v>
       </c>
       <c r="E315" t="n">
@@ -10485,11 +10473,11 @@
         <v>1542.590000000001</v>
       </c>
       <c r="H315" t="n">
-        <v>0.0934219856676872</v>
+        <v>0.09342198566768722</v>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" t="n">
         <v>314</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -10497,10 +10485,10 @@
           <t>2046-03</t>
         </is>
       </c>
-      <c r="C316" s="155" t="n">
+      <c r="C316" s="154" t="n">
         <v>35717</v>
       </c>
-      <c r="D316" s="73" t="n">
+      <c r="D316" s="72" t="n">
         <v>2051.31</v>
       </c>
       <c r="E316" t="n">
@@ -10513,11 +10501,11 @@
         <v>1795.396666666667</v>
       </c>
       <c r="H316" t="n">
-        <v>0.0900345928888495</v>
+        <v>0.09003459288884952</v>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" t="n">
         <v>315</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -10525,10 +10513,10 @@
           <t>2046-04</t>
         </is>
       </c>
-      <c r="C317" s="95" t="n">
+      <c r="C317" s="94" t="n">
         <v>30774.56</v>
       </c>
-      <c r="D317" s="79" t="n">
+      <c r="D317" s="78" t="n">
         <v>1308.14</v>
       </c>
       <c r="E317" t="n">
@@ -10541,11 +10529,11 @@
         <v>1636.940000000001</v>
       </c>
       <c r="H317" t="n">
-        <v>-0.1383778032869501</v>
+        <v>-0.1383778032869502</v>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" t="n">
         <v>316</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -10553,10 +10541,10 @@
           <t>2046-05</t>
         </is>
       </c>
-      <c r="C318" s="39" t="n">
+      <c r="C318" s="38" t="n">
         <v>32572.59</v>
       </c>
-      <c r="D318" s="192" t="n">
+      <c r="D318" s="191" t="n">
         <v>1242.17</v>
       </c>
       <c r="E318" t="n">
@@ -10569,11 +10557,11 @@
         <v>1533.873333333334</v>
       </c>
       <c r="H318" t="n">
-        <v>0.0584258556418026</v>
+        <v>0.05842585564180269</v>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" t="n">
         <v>317</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -10581,10 +10569,10 @@
           <t>2046-06</t>
         </is>
       </c>
-      <c r="C319" s="187" t="n">
+      <c r="C319" s="186" t="n">
         <v>23570.3</v>
       </c>
-      <c r="D319" s="23" t="n">
+      <c r="D319" s="22" t="n">
         <v>1671.13</v>
       </c>
       <c r="E319" t="n">
@@ -10601,7 +10589,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" t="n">
         <v>318</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -10609,10 +10597,10 @@
           <t>2046-07</t>
         </is>
       </c>
-      <c r="C320" s="100" t="n">
+      <c r="C320" s="99" t="n">
         <v>31182.8</v>
       </c>
-      <c r="D320" s="127" t="n">
+      <c r="D320" s="126" t="n">
         <v>1712.29</v>
       </c>
       <c r="E320" t="n">
@@ -10625,11 +10613,11 @@
         <v>1541.863333333334</v>
       </c>
       <c r="H320" t="n">
-        <v>0.3229700088670912</v>
+        <v>0.3229700088670913</v>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" t="n">
         <v>319</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -10637,10 +10625,10 @@
           <t>2046-08</t>
         </is>
       </c>
-      <c r="C321" s="60" t="n">
+      <c r="C321" s="59" t="n">
         <v>31068.26</v>
       </c>
-      <c r="D321" s="190" t="n">
+      <c r="D321" s="189" t="n">
         <v>2213.47</v>
       </c>
       <c r="E321" t="n">
@@ -10653,11 +10641,11 @@
         <v>1865.63</v>
       </c>
       <c r="H321" t="n">
-        <v>-0.0036731788036995</v>
+        <v>-0.003673178803699551</v>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" t="n">
         <v>320</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -10665,10 +10653,10 @@
           <t>2046-09</t>
         </is>
       </c>
-      <c r="C322" s="19" t="n">
+      <c r="C322" s="18" t="n">
         <v>27921.11</v>
       </c>
-      <c r="D322" s="146" t="n">
+      <c r="D322" s="145" t="n">
         <v>1152.56</v>
       </c>
       <c r="E322" t="n">
@@ -10681,11 +10669,11 @@
         <v>1692.773333333334</v>
       </c>
       <c r="H322" t="n">
-        <v>-0.1012979162656678</v>
+        <v>-0.1012979162656679</v>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" t="n">
         <v>321</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -10693,10 +10681,10 @@
           <t>2046-10</t>
         </is>
       </c>
-      <c r="C323" s="14" t="n">
+      <c r="C323" s="13" t="n">
         <v>29643.29</v>
       </c>
-      <c r="D323" s="41" t="n">
+      <c r="D323" s="40" t="n">
         <v>2263.69</v>
       </c>
       <c r="E323" t="n">
@@ -10706,14 +10694,14 @@
         <v>2775.903225806452</v>
       </c>
       <c r="G323" t="n">
-        <v>1876.573333333333</v>
+        <v>1876.573333333334</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0616802125703455</v>
+        <v>0.06168021257034551</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" t="n">
         <v>322</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -10721,10 +10709,10 @@
           <t>2046-11</t>
         </is>
       </c>
-      <c r="C324" s="127" t="n">
+      <c r="C324" s="126" t="n">
         <v>28623.84</v>
       </c>
-      <c r="D324" s="10" t="n">
+      <c r="D324" s="9" t="n">
         <v>1915.11</v>
       </c>
       <c r="E324" t="n">
@@ -10741,7 +10729,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" t="n">
         <v>323</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -10749,10 +10737,10 @@
           <t>2046-12</t>
         </is>
       </c>
-      <c r="C325" s="20" t="n">
+      <c r="C325" s="19" t="n">
         <v>29802.97</v>
       </c>
-      <c r="D325" s="28" t="n">
+      <c r="D325" s="27" t="n">
         <v>1733.16</v>
       </c>
       <c r="E325" t="n">
@@ -10765,11 +10753,11 @@
         <v>1970.653333333334</v>
       </c>
       <c r="H325" t="n">
-        <v>0.0411939837561976</v>
+        <v>0.04119398375619765</v>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" t="n">
         <v>324</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -10777,10 +10765,10 @@
           <t>2047-01</t>
         </is>
       </c>
-      <c r="C326" s="26" t="n">
+      <c r="C326" s="25" t="n">
         <v>31448.7</v>
       </c>
-      <c r="D326" s="82" t="n">
+      <c r="D326" s="81" t="n">
         <v>1422.22</v>
       </c>
       <c r="E326" t="n">
@@ -10793,11 +10781,11 @@
         <v>1690.163333333334</v>
       </c>
       <c r="H326" t="n">
-        <v>0.0552203354229461</v>
+        <v>0.05522033542294613</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" t="n">
         <v>325</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -10805,10 +10793,10 @@
           <t>2047-02</t>
         </is>
       </c>
-      <c r="C327" s="37" t="n">
+      <c r="C327" s="36" t="n">
         <v>27719.81</v>
       </c>
-      <c r="D327" s="75" t="n">
+      <c r="D327" s="74" t="n">
         <v>1762.42</v>
       </c>
       <c r="E327" t="n">
@@ -10825,7 +10813,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" t="n">
         <v>326</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -10833,10 +10821,10 @@
           <t>2047-03</t>
         </is>
       </c>
-      <c r="C328" s="106" t="n">
+      <c r="C328" s="105" t="n">
         <v>35454.26</v>
       </c>
-      <c r="D328" s="3" t="n">
+      <c r="D328" s="2" t="n">
         <v>1495.51</v>
       </c>
       <c r="E328" t="n">
@@ -10853,7 +10841,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" t="n">
         <v>327</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -10861,10 +10849,10 @@
           <t>2047-04</t>
         </is>
       </c>
-      <c r="C329" s="102" t="n">
+      <c r="C329" s="101" t="n">
         <v>29930.82</v>
       </c>
-      <c r="D329" s="182" t="n">
+      <c r="D329" s="181" t="n">
         <v>1679.17</v>
       </c>
       <c r="E329" t="n">
@@ -10877,22 +10865,22 @@
         <v>1645.700000000001</v>
       </c>
       <c r="H329" t="n">
-        <v>-0.1557905876472954</v>
+        <v>-0.1557905876472955</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" t="n">
         <v>328</v>
       </c>
-      <c r="B330" s="116" t="inlineStr">
+      <c r="B330" s="115" t="inlineStr">
         <is>
           <t>2047-05</t>
         </is>
       </c>
-      <c r="C330" s="177" t="n">
+      <c r="C330" s="176" t="n">
         <v>17422.03</v>
       </c>
-      <c r="D330" s="69" t="n">
+      <c r="D330" s="68" t="n">
         <v>912.72</v>
       </c>
       <c r="E330" t="n">
@@ -10905,7 +10893,7 @@
         <v>1362.466666666667</v>
       </c>
       <c r="H330" t="n">
-        <v>-0.4179233980225065</v>
+        <v>-0.4179233980225066</v>
       </c>
     </row>
   </sheetData>
